--- a/KindleClippings.ConsoleApp/GooglePhotoAlbums.xlsx
+++ b/KindleClippings.ConsoleApp/GooglePhotoAlbums.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alber\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alber\Documents\Visual Studio 2022\Projects\AlbertoBizzini\KindleClippings.ConsoleApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F3E3F47215EF076B88AD44458C2D1E376A694A1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B712A2BE-5B5D-483D-8024-2D25120135DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1105">
   <si>
     <t>Data da</t>
   </si>
@@ -3332,6 +3332,9 @@
   </si>
   <si>
     <t>Seoul</t>
+  </si>
+  <si>
+    <t>https://photos.app.goo.gl/t8aGFFQBePiGKwCG6</t>
   </si>
 </sst>
 </file>
@@ -3815,7 +3818,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3828,6 +3831,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Colore 1" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3900,11 +3904,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabella1" displayName="Tabella1" ref="A1:L315" totalsRowShown="0">
   <autoFilter ref="A1:L315" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L315">
-    <sortCondition ref="A2:A315"/>
-    <sortCondition ref="B2:B315"/>
-    <sortCondition ref="C2:C315"/>
-  </sortState>
   <tableColumns count="12">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Data da" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Data a" dataDxfId="1"/>
@@ -4482,13 +4481,13 @@
     </row>
     <row r="11" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
-        <v>39958</v>
+        <v>39957</v>
       </c>
       <c r="B11" s="4">
-        <v>39958</v>
+        <v>39957</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>1011</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -4511,22 +4510,22 @@
       <c r="J11">
         <v>-122.4194</v>
       </c>
-      <c r="K11" t="s">
-        <v>52</v>
+      <c r="K11" s="6" t="s">
+        <v>1012</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>53</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
-        <v>39959</v>
+        <v>39958</v>
       </c>
       <c r="B12" s="4">
-        <v>39959</v>
+        <v>39958</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -4538,33 +4537,33 @@
         <v>1083</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I12">
-        <v>38.939900000000002</v>
+        <v>37.774900000000002</v>
       </c>
       <c r="J12">
-        <v>-119.9772</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>56</v>
+        <v>-122.4194</v>
+      </c>
+      <c r="K12" t="s">
+        <v>52</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
-        <v>39960</v>
+        <v>39959</v>
       </c>
       <c r="B13" s="4">
-        <v>39960</v>
+        <v>39959</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -4576,33 +4575,33 @@
         <v>1083</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I13">
-        <v>38.255699999999997</v>
+        <v>38.939900000000002</v>
       </c>
       <c r="J13">
-        <v>-119.2313</v>
-      </c>
-      <c r="K13" t="s">
-        <v>60</v>
+        <v>-119.9772</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
-        <v>39961</v>
+        <v>39960</v>
       </c>
       <c r="B14" s="4">
-        <v>39961</v>
+        <v>39960</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -4614,33 +4613,33 @@
         <v>1083</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I14">
-        <v>37.745600000000003</v>
+        <v>38.255699999999997</v>
       </c>
       <c r="J14">
-        <v>-119.5936</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>64</v>
+        <v>-119.2313</v>
+      </c>
+      <c r="K14" t="s">
+        <v>60</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
-        <v>39962</v>
+        <v>39961</v>
       </c>
       <c r="B15" s="4">
-        <v>39962</v>
+        <v>39961</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -4652,33 +4651,33 @@
         <v>1083</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I15">
-        <v>36.438800000000001</v>
+        <v>37.745600000000003</v>
       </c>
       <c r="J15">
-        <v>-118.9045</v>
+        <v>-119.5936</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
-        <v>39963</v>
+        <v>39962</v>
       </c>
       <c r="B16" s="4">
-        <v>39963</v>
+        <v>39962</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -4690,33 +4689,33 @@
         <v>1083</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I16">
-        <v>36.456099999999999</v>
+        <v>36.438800000000001</v>
       </c>
       <c r="J16">
-        <v>-116.8656</v>
+        <v>-118.9045</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
-        <v>39964</v>
+        <v>39963</v>
       </c>
       <c r="B17" s="4">
-        <v>39964</v>
+        <v>39963</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -4740,10 +4739,10 @@
         <v>-116.8656</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -4754,7 +4753,7 @@
         <v>39964</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -4766,33 +4765,33 @@
         <v>1083</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I18">
-        <v>36.169899999999998</v>
+        <v>36.456099999999999</v>
       </c>
       <c r="J18">
-        <v>-115.13979999999999</v>
+        <v>-116.8656</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
-        <v>39965</v>
+        <v>39964</v>
       </c>
       <c r="B19" s="4">
-        <v>39965</v>
+        <v>39964</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -4804,33 +4803,33 @@
         <v>1083</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I19">
-        <v>37.188899999999997</v>
+        <v>36.169899999999998</v>
       </c>
       <c r="J19">
-        <v>-112.9986</v>
+        <v>-115.13979999999999</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
-        <v>39966</v>
+        <v>39965</v>
       </c>
       <c r="B20" s="4">
-        <v>39966</v>
+        <v>39965</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -4842,33 +4841,33 @@
         <v>1083</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I20">
-        <v>37.628300000000003</v>
+        <v>37.188899999999997</v>
       </c>
       <c r="J20">
-        <v>-112.1677</v>
+        <v>-112.9986</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
-        <v>39967</v>
+        <v>39966</v>
       </c>
       <c r="B21" s="4">
-        <v>39967</v>
+        <v>39966</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -4880,33 +4879,33 @@
         <v>1083</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I21">
-        <v>36.914700000000003</v>
+        <v>37.628300000000003</v>
       </c>
       <c r="J21">
-        <v>-111.4558</v>
+        <v>-112.1677</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
-        <v>39968</v>
+        <v>39967</v>
       </c>
       <c r="B22" s="4">
-        <v>39968</v>
+        <v>39967</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -4918,33 +4917,33 @@
         <v>1083</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I22">
-        <v>36.727800000000002</v>
+        <v>36.914700000000003</v>
       </c>
       <c r="J22">
-        <v>-110.2546</v>
+        <v>-111.4558</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>39969</v>
+        <v>39968</v>
       </c>
       <c r="B23" s="4">
-        <v>39969</v>
+        <v>39968</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -4956,98 +4955,98 @@
         <v>1083</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I23">
-        <v>36.054400000000001</v>
+        <v>36.727800000000002</v>
       </c>
       <c r="J23">
-        <v>-112.1401</v>
+        <v>-110.2546</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>40080</v>
+        <v>39969</v>
       </c>
       <c r="B24" s="4">
-        <v>40086</v>
+        <v>39969</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H24" t="s">
-        <v>1085</v>
+        <v>98</v>
       </c>
       <c r="I24">
-        <v>48.8566</v>
+        <v>36.054400000000001</v>
       </c>
       <c r="J24">
-        <v>2.3521999999999998</v>
-      </c>
-      <c r="K24" t="s">
-        <v>103</v>
+        <v>-112.1401</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>40181</v>
+        <v>40080</v>
       </c>
       <c r="B25" s="4">
-        <v>42610</v>
+        <v>40086</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H25" t="s">
-        <v>106</v>
+        <v>1085</v>
       </c>
       <c r="I25">
-        <v>21.402200000000001</v>
+        <v>48.8566</v>
       </c>
       <c r="J25">
-        <v>-157.73939999999999</v>
+        <v>2.3521999999999998</v>
       </c>
       <c r="K25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -6366,6 +6365,30 @@
       <c r="C64" t="s">
         <v>241</v>
       </c>
+      <c r="D64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64">
+        <v>44.509300000000003</v>
+      </c>
+      <c r="J64">
+        <v>11.3589</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>1104</v>
+      </c>
       <c r="L64" s="5" t="s">
         <v>242</v>
       </c>
@@ -8421,13 +8444,13 @@
     </row>
     <row r="122" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
-        <v>42611</v>
+        <v>42610</v>
       </c>
       <c r="B122" s="4">
-        <v>42612</v>
+        <v>42610</v>
       </c>
       <c r="C122" t="s">
-        <v>444</v>
+        <v>105</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -8439,33 +8462,33 @@
         <v>1083</v>
       </c>
       <c r="G122" t="s">
-        <v>445</v>
+        <v>106</v>
       </c>
       <c r="H122" t="s">
-        <v>445</v>
+        <v>106</v>
       </c>
       <c r="I122">
-        <v>22.205300000000001</v>
+        <v>21.402200000000001</v>
       </c>
       <c r="J122">
-        <v>-159.5</v>
+        <v>-157.73939999999999</v>
       </c>
       <c r="K122" t="s">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="L122" s="5" t="s">
-        <v>447</v>
+        <v>108</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
+        <v>42611</v>
+      </c>
+      <c r="B123" s="4">
         <v>42612</v>
       </c>
-      <c r="B123" s="4">
-        <v>42613</v>
-      </c>
       <c r="C123" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -8477,33 +8500,33 @@
         <v>1083</v>
       </c>
       <c r="G123" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H123" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I123">
-        <v>21.958600000000001</v>
+        <v>22.205300000000001</v>
       </c>
       <c r="J123">
-        <v>-159.6688</v>
+        <v>-159.5</v>
       </c>
       <c r="K123" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="L123" s="5" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
+        <v>42612</v>
+      </c>
+      <c r="B124" s="4">
         <v>42613</v>
       </c>
-      <c r="B124" s="4">
-        <v>42614</v>
-      </c>
       <c r="C124" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -8515,33 +8538,33 @@
         <v>1083</v>
       </c>
       <c r="G124" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H124" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="I124">
-        <v>21.906700000000001</v>
+        <v>21.958600000000001</v>
       </c>
       <c r="J124">
-        <v>-159.4691</v>
+        <v>-159.6688</v>
       </c>
       <c r="K124" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L124" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
-        <v>42615</v>
+        <v>42613</v>
       </c>
       <c r="B125" s="4">
-        <v>42615</v>
+        <v>42614</v>
       </c>
       <c r="C125" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -8553,22 +8576,22 @@
         <v>1083</v>
       </c>
       <c r="G125" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H125" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="I125">
-        <v>20.878299999999999</v>
+        <v>21.906700000000001</v>
       </c>
       <c r="J125">
-        <v>-156.6825</v>
+        <v>-159.4691</v>
       </c>
       <c r="K125" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="L125" s="5" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -8576,10 +8599,10 @@
         <v>42615</v>
       </c>
       <c r="B126" s="4">
-        <v>42616</v>
+        <v>42615</v>
       </c>
       <c r="C126" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
@@ -8591,33 +8614,33 @@
         <v>1083</v>
       </c>
       <c r="G126" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H126" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="I126">
-        <v>20.752400000000002</v>
+        <v>20.878299999999999</v>
       </c>
       <c r="J126">
-        <v>-155.9879</v>
+        <v>-156.6825</v>
       </c>
       <c r="K126" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="L126" s="5" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
+        <v>42615</v>
+      </c>
+      <c r="B127" s="4">
         <v>42616</v>
       </c>
-      <c r="B127" s="4">
-        <v>42617</v>
-      </c>
       <c r="C127" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D127" t="s">
         <v>32</v>
@@ -8629,33 +8652,33 @@
         <v>1083</v>
       </c>
       <c r="G127" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H127" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="I127">
-        <v>20.764399999999998</v>
+        <v>20.752400000000002</v>
       </c>
       <c r="J127">
-        <v>-156.44499999999999</v>
+        <v>-155.9879</v>
       </c>
       <c r="K127" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="L127" s="5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
+        <v>42616</v>
+      </c>
+      <c r="B128" s="4">
         <v>42617</v>
       </c>
-      <c r="B128" s="4">
-        <v>42618</v>
-      </c>
       <c r="C128" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D128" t="s">
         <v>32</v>
@@ -8667,33 +8690,33 @@
         <v>1083</v>
       </c>
       <c r="G128" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H128" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I128">
-        <v>20.889299999999999</v>
+        <v>20.764399999999998</v>
       </c>
       <c r="J128">
-        <v>-156.47290000000001</v>
+        <v>-156.44499999999999</v>
       </c>
       <c r="K128" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="L128" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
+        <v>42617</v>
+      </c>
+      <c r="B129" s="4">
         <v>42618</v>
       </c>
-      <c r="B129" s="4">
-        <v>42619</v>
-      </c>
       <c r="C129" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D129" t="s">
         <v>32</v>
@@ -8705,33 +8728,33 @@
         <v>1083</v>
       </c>
       <c r="G129" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H129" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I129">
-        <v>19.639900000000001</v>
+        <v>20.889299999999999</v>
       </c>
       <c r="J129">
-        <v>-155.99690000000001</v>
+        <v>-156.47290000000001</v>
       </c>
       <c r="K129" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L129" s="5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
+        <v>42618</v>
+      </c>
+      <c r="B130" s="4">
         <v>42619</v>
       </c>
-      <c r="B130" s="4">
-        <v>42620</v>
-      </c>
       <c r="C130" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D130" t="s">
         <v>32</v>
@@ -8743,33 +8766,33 @@
         <v>1083</v>
       </c>
       <c r="G130" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H130" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I130">
-        <v>19.430800000000001</v>
+        <v>19.639900000000001</v>
       </c>
       <c r="J130">
-        <v>-155.24090000000001</v>
+        <v>-155.99690000000001</v>
       </c>
       <c r="K130" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="L130" s="5" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="131" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
-        <v>42620</v>
+        <v>42619</v>
       </c>
       <c r="B131" s="4">
         <v>42620</v>
       </c>
       <c r="C131" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D131" t="s">
         <v>32</v>
@@ -8781,33 +8804,33 @@
         <v>1083</v>
       </c>
       <c r="G131" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H131" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="I131">
-        <v>19.7074</v>
+        <v>19.430800000000001</v>
       </c>
       <c r="J131">
-        <v>-155.08160000000001</v>
+        <v>-155.24090000000001</v>
       </c>
       <c r="K131" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="L131" s="5" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
-        <v>42621</v>
+        <v>42620</v>
       </c>
       <c r="B132" s="4">
-        <v>42621</v>
+        <v>42620</v>
       </c>
       <c r="C132" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D132" t="s">
         <v>32</v>
@@ -8819,33 +8842,33 @@
         <v>1083</v>
       </c>
       <c r="G132" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="H132" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="I132">
-        <v>19.639900000000001</v>
+        <v>19.7074</v>
       </c>
       <c r="J132">
-        <v>-155.99690000000001</v>
+        <v>-155.08160000000001</v>
       </c>
       <c r="K132" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L132" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
-        <v>42622</v>
+        <v>42621</v>
       </c>
       <c r="B133" s="4">
-        <v>42622</v>
+        <v>42621</v>
       </c>
       <c r="C133" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
@@ -8857,33 +8880,33 @@
         <v>1083</v>
       </c>
       <c r="G133" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="H133" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="I133">
-        <v>19.4969</v>
+        <v>19.639900000000001</v>
       </c>
       <c r="J133">
-        <v>-155.92169999999999</v>
+        <v>-155.99690000000001</v>
       </c>
       <c r="K133" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L133" s="5" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="134" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
-        <v>42623</v>
+        <v>42622</v>
       </c>
       <c r="B134" s="4">
-        <v>42625</v>
+        <v>42622</v>
       </c>
       <c r="C134" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D134" t="s">
         <v>32</v>
@@ -8895,71 +8918,71 @@
         <v>1083</v>
       </c>
       <c r="G134" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="H134" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="I134">
-        <v>19.7074</v>
+        <v>19.4969</v>
       </c>
       <c r="J134">
-        <v>-155.08160000000001</v>
+        <v>-155.92169999999999</v>
       </c>
       <c r="K134" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
-        <v>42672</v>
+        <v>42623</v>
       </c>
       <c r="B135" s="4">
-        <v>42673</v>
+        <v>42625</v>
       </c>
       <c r="C135" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D135" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E135" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F135" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="G135" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="H135" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="I135">
-        <v>46.193399999999997</v>
+        <v>19.7074</v>
       </c>
       <c r="J135">
-        <v>11.133100000000001</v>
+        <v>-155.08160000000001</v>
       </c>
       <c r="K135" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
-        <v>42686</v>
+        <v>42672</v>
       </c>
       <c r="B136" s="4">
-        <v>42686</v>
+        <v>42673</v>
       </c>
       <c r="C136" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D136" t="s">
         <v>13</v>
@@ -8971,161 +8994,161 @@
         <v>1078</v>
       </c>
       <c r="G136" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H136" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I136">
-        <v>44.258000000000003</v>
+        <v>46.193399999999997</v>
       </c>
       <c r="J136">
-        <v>11.1524</v>
+        <v>11.133100000000001</v>
       </c>
       <c r="K136" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="L136" s="5" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
-        <v>42743</v>
+        <v>42686</v>
       </c>
       <c r="B137" s="4">
-        <v>42743</v>
+        <v>42686</v>
       </c>
       <c r="C137" t="s">
-        <v>502</v>
-      </c>
-      <c r="D137" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="D137" t="s">
         <v>13</v>
       </c>
-      <c r="E137" s="6" t="s">
+      <c r="E137" t="s">
         <v>14</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="F137" t="s">
         <v>1078</v>
       </c>
-      <c r="G137" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>19</v>
+      <c r="G137" t="s">
+        <v>499</v>
+      </c>
+      <c r="H137" t="s">
+        <v>499</v>
       </c>
       <c r="I137">
-        <v>44.509300000000003</v>
+        <v>44.258000000000003</v>
       </c>
       <c r="J137">
-        <v>11.3589</v>
+        <v>11.1524</v>
       </c>
       <c r="K137" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L137" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
-        <v>42749</v>
+        <v>42743</v>
       </c>
       <c r="B138" s="4">
-        <v>42750</v>
+        <v>42743</v>
       </c>
       <c r="C138" t="s">
-        <v>505</v>
-      </c>
-      <c r="D138" t="s">
+        <v>502</v>
+      </c>
+      <c r="D138" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="6" t="s">
         <v>1078</v>
       </c>
-      <c r="G138" t="s">
-        <v>506</v>
-      </c>
-      <c r="H138" t="s">
-        <v>1092</v>
+      <c r="G138" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="I138">
-        <v>41.902799999999999</v>
+        <v>44.509300000000003</v>
       </c>
       <c r="J138">
-        <v>12.4964</v>
-      </c>
-      <c r="K138" s="6" t="s">
-        <v>507</v>
+        <v>11.3589</v>
+      </c>
+      <c r="K138" t="s">
+        <v>503</v>
       </c>
       <c r="L138" s="5" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
-        <v>42810</v>
+        <v>42749</v>
       </c>
       <c r="B139" s="4">
-        <v>42810</v>
+        <v>42750</v>
       </c>
       <c r="C139" t="s">
-        <v>509</v>
+        <v>505</v>
+      </c>
+      <c r="D139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" t="s">
+        <v>14</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G139" t="s">
+        <v>506</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I139">
+        <v>41.902799999999999</v>
+      </c>
+      <c r="J139">
+        <v>12.4964</v>
+      </c>
+      <c r="K139" s="6" t="s">
+        <v>507</v>
       </c>
       <c r="L139" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
-        <v>42816</v>
+        <v>42810</v>
       </c>
       <c r="B140" s="4">
-        <v>42817</v>
+        <v>42810</v>
       </c>
       <c r="C140" t="s">
-        <v>511</v>
-      </c>
-      <c r="D140" t="s">
-        <v>164</v>
-      </c>
-      <c r="E140" t="s">
-        <v>165</v>
-      </c>
-      <c r="F140" t="s">
-        <v>1087</v>
-      </c>
-      <c r="G140" t="s">
-        <v>166</v>
-      </c>
-      <c r="H140" t="s">
-        <v>166</v>
-      </c>
-      <c r="I140">
-        <v>35.676200000000001</v>
-      </c>
-      <c r="J140">
-        <v>139.65029999999999</v>
-      </c>
-      <c r="K140" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="L140" s="5" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
+        <v>42816</v>
+      </c>
+      <c r="B141" s="4">
         <v>42817</v>
       </c>
-      <c r="B141" s="4">
-        <v>42818</v>
-      </c>
       <c r="C141" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D141" t="s">
         <v>164</v>
@@ -9149,21 +9172,21 @@
         <v>139.65029999999999</v>
       </c>
       <c r="K141" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L141" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="142" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
+        <v>42817</v>
+      </c>
+      <c r="B142" s="4">
         <v>42818</v>
       </c>
-      <c r="B142" s="4">
-        <v>42819</v>
-      </c>
       <c r="C142" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D142" t="s">
         <v>164</v>
@@ -9175,33 +9198,33 @@
         <v>1087</v>
       </c>
       <c r="G142" t="s">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="H142" t="s">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="I142">
-        <v>34.348300000000002</v>
+        <v>35.676200000000001</v>
       </c>
       <c r="J142">
-        <v>132.33179999999999</v>
+        <v>139.65029999999999</v>
       </c>
       <c r="K142" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="L142" s="5" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
-        <v>42820</v>
+        <v>42818</v>
       </c>
       <c r="B143" s="4">
-        <v>42820</v>
+        <v>42819</v>
       </c>
       <c r="C143" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D143" t="s">
         <v>164</v>
@@ -9213,33 +9236,33 @@
         <v>1087</v>
       </c>
       <c r="G143" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H143" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="I143">
-        <v>33.512799999999999</v>
+        <v>34.348300000000002</v>
       </c>
       <c r="J143">
-        <v>130.5239</v>
+        <v>132.33179999999999</v>
       </c>
       <c r="K143" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="L143" s="5" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
-        <v>42821</v>
+        <v>42820</v>
       </c>
       <c r="B144" s="4">
-        <v>42821</v>
+        <v>42820</v>
       </c>
       <c r="C144" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D144" t="s">
         <v>164</v>
@@ -9251,33 +9274,33 @@
         <v>1087</v>
       </c>
       <c r="G144" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H144" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I144">
-        <v>33.284599999999998</v>
+        <v>33.512799999999999</v>
       </c>
       <c r="J144">
-        <v>131.49100000000001</v>
+        <v>130.5239</v>
       </c>
       <c r="K144" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="L144" s="5" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="145" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
-        <v>42822</v>
+        <v>42821</v>
       </c>
       <c r="B145" s="4">
-        <v>42822</v>
+        <v>42821</v>
       </c>
       <c r="C145" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D145" t="s">
         <v>164</v>
@@ -9289,33 +9312,33 @@
         <v>1087</v>
       </c>
       <c r="G145" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H145" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I145">
-        <v>31.596599999999999</v>
+        <v>33.284599999999998</v>
       </c>
       <c r="J145">
-        <v>130.55709999999999</v>
+        <v>131.49100000000001</v>
       </c>
       <c r="K145" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="L145" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
-        <v>42823</v>
+        <v>42822</v>
       </c>
       <c r="B146" s="4">
-        <v>42823</v>
+        <v>42822</v>
       </c>
       <c r="C146" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D146" t="s">
         <v>164</v>
@@ -9327,33 +9350,33 @@
         <v>1087</v>
       </c>
       <c r="G146" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="H146" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I146">
-        <v>33.1036</v>
+        <v>31.596599999999999</v>
       </c>
       <c r="J146">
-        <v>130.09889999999999</v>
+        <v>130.55709999999999</v>
       </c>
       <c r="K146" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="L146" s="5" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
-        <v>42824</v>
+        <v>42823</v>
       </c>
       <c r="B147" s="4">
-        <v>42824</v>
+        <v>42823</v>
       </c>
       <c r="C147" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D147" t="s">
         <v>164</v>
@@ -9365,33 +9388,33 @@
         <v>1087</v>
       </c>
       <c r="G147" t="s">
-        <v>210</v>
+        <v>534</v>
       </c>
       <c r="H147" t="s">
-        <v>210</v>
+        <v>534</v>
       </c>
       <c r="I147">
-        <v>34.212000000000003</v>
+        <v>33.1036</v>
       </c>
       <c r="J147">
-        <v>135.5866</v>
+        <v>130.09889999999999</v>
       </c>
       <c r="K147" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="L147" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="148" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
-        <v>42825</v>
+        <v>42824</v>
       </c>
       <c r="B148" s="4">
-        <v>42825</v>
+        <v>42824</v>
       </c>
       <c r="C148" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D148" t="s">
         <v>164</v>
@@ -9403,33 +9426,33 @@
         <v>1087</v>
       </c>
       <c r="G148" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="H148" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="I148">
-        <v>35.011600000000001</v>
+        <v>34.212000000000003</v>
       </c>
       <c r="J148">
-        <v>135.7681</v>
+        <v>135.5866</v>
       </c>
       <c r="K148" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="L148" s="5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
-        <v>42826</v>
+        <v>42825</v>
       </c>
       <c r="B149" s="4">
-        <v>42826</v>
+        <v>42825</v>
       </c>
       <c r="C149" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D149" t="s">
         <v>164</v>
@@ -9453,21 +9476,21 @@
         <v>135.7681</v>
       </c>
       <c r="K149" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L149" s="5" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="150" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
-        <v>42827</v>
+        <v>42826</v>
       </c>
       <c r="B150" s="4">
-        <v>42827</v>
+        <v>42826</v>
       </c>
       <c r="C150" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D150" t="s">
         <v>164</v>
@@ -9491,10 +9514,10 @@
         <v>135.7681</v>
       </c>
       <c r="K150" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="L150" s="5" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -9502,10 +9525,10 @@
         <v>42827</v>
       </c>
       <c r="B151" s="4">
-        <v>42829</v>
+        <v>42827</v>
       </c>
       <c r="C151" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D151" t="s">
         <v>164</v>
@@ -9517,33 +9540,33 @@
         <v>1087</v>
       </c>
       <c r="G151" t="s">
-        <v>550</v>
+        <v>199</v>
       </c>
       <c r="H151" t="s">
-        <v>550</v>
+        <v>199</v>
       </c>
       <c r="I151">
-        <v>34.884500000000003</v>
+        <v>35.011600000000001</v>
       </c>
       <c r="J151">
-        <v>135.7997</v>
+        <v>135.7681</v>
       </c>
       <c r="K151" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="L151" s="5" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
-        <v>42828</v>
+        <v>42827</v>
       </c>
       <c r="B152" s="4">
-        <v>42828</v>
+        <v>42829</v>
       </c>
       <c r="C152" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D152" t="s">
         <v>164</v>
@@ -9567,21 +9590,21 @@
         <v>135.7997</v>
       </c>
       <c r="K152" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="L152" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
-        <v>42830</v>
+        <v>42828</v>
       </c>
       <c r="B153" s="4">
-        <v>42830</v>
+        <v>42828</v>
       </c>
       <c r="C153" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D153" t="s">
         <v>164</v>
@@ -9593,22 +9616,22 @@
         <v>1087</v>
       </c>
       <c r="G153" t="s">
-        <v>199</v>
+        <v>550</v>
       </c>
       <c r="H153" t="s">
-        <v>199</v>
+        <v>550</v>
       </c>
       <c r="I153">
-        <v>35.011600000000001</v>
+        <v>34.884500000000003</v>
       </c>
       <c r="J153">
-        <v>135.7681</v>
+        <v>135.7997</v>
       </c>
       <c r="K153" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="L153" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -9619,7 +9642,7 @@
         <v>42830</v>
       </c>
       <c r="C154" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D154" t="s">
         <v>164</v>
@@ -9631,30 +9654,33 @@
         <v>1087</v>
       </c>
       <c r="G154" t="s">
-        <v>560</v>
+        <v>199</v>
       </c>
       <c r="H154" t="s">
-        <v>560</v>
+        <v>199</v>
       </c>
       <c r="I154">
-        <v>35.121000000000002</v>
+        <v>35.011600000000001</v>
       </c>
       <c r="J154">
-        <v>136.09559999999999</v>
+        <v>135.7681</v>
+      </c>
+      <c r="K154" t="s">
+        <v>557</v>
       </c>
       <c r="L154" s="5" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="155" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
-        <v>42831</v>
+        <v>42830</v>
       </c>
       <c r="B155" s="4">
-        <v>42831</v>
+        <v>42830</v>
       </c>
       <c r="C155" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D155" t="s">
         <v>164</v>
@@ -9666,33 +9692,30 @@
         <v>1087</v>
       </c>
       <c r="G155" t="s">
-        <v>199</v>
+        <v>560</v>
       </c>
       <c r="H155" t="s">
-        <v>199</v>
+        <v>560</v>
       </c>
       <c r="I155">
-        <v>35.011600000000001</v>
+        <v>35.121000000000002</v>
       </c>
       <c r="J155">
-        <v>135.7681</v>
-      </c>
-      <c r="K155" t="s">
-        <v>563</v>
+        <v>136.09559999999999</v>
       </c>
       <c r="L155" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
-        <v>42832</v>
+        <v>42831</v>
       </c>
       <c r="B156" s="4">
-        <v>42833</v>
+        <v>42831</v>
       </c>
       <c r="C156" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D156" t="s">
         <v>164</v>
@@ -9704,33 +9727,33 @@
         <v>1087</v>
       </c>
       <c r="G156" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="H156" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="I156">
-        <v>35.676200000000001</v>
+        <v>35.011600000000001</v>
       </c>
       <c r="J156">
-        <v>139.65029999999999</v>
+        <v>135.7681</v>
       </c>
       <c r="K156" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="L156" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
-        <v>42834</v>
+        <v>42832</v>
       </c>
       <c r="B157" s="4">
-        <v>42835</v>
+        <v>42833</v>
       </c>
       <c r="C157" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D157" t="s">
         <v>164</v>
@@ -9742,33 +9765,33 @@
         <v>1087</v>
       </c>
       <c r="G157" t="s">
-        <v>569</v>
+        <v>166</v>
       </c>
       <c r="H157" t="s">
-        <v>569</v>
+        <v>166</v>
       </c>
       <c r="I157">
-        <v>35.655799999999999</v>
+        <v>35.676200000000001</v>
       </c>
       <c r="J157">
-        <v>139.3389</v>
+        <v>139.65029999999999</v>
       </c>
       <c r="K157" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="L157" s="5" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
-        <v>42836</v>
+        <v>42834</v>
       </c>
       <c r="B158" s="4">
-        <v>42837</v>
+        <v>42835</v>
       </c>
       <c r="C158" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D158" t="s">
         <v>164</v>
@@ -9780,123 +9803,123 @@
         <v>1087</v>
       </c>
       <c r="G158" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="H158" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I158">
-        <v>35.776699999999998</v>
+        <v>35.655799999999999</v>
       </c>
       <c r="J158">
-        <v>140.31890000000001</v>
+        <v>139.3389</v>
       </c>
       <c r="K158" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="L158" s="5" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
-        <v>42889</v>
+        <v>42836</v>
       </c>
       <c r="B159" s="4">
-        <v>42889</v>
+        <v>42837</v>
       </c>
       <c r="C159" t="s">
-        <v>576</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>19</v>
+        <v>572</v>
+      </c>
+      <c r="D159" t="s">
+        <v>164</v>
+      </c>
+      <c r="E159" t="s">
+        <v>165</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G159" t="s">
+        <v>573</v>
+      </c>
+      <c r="H159" t="s">
+        <v>573</v>
       </c>
       <c r="I159">
-        <v>44.509300000000003</v>
+        <v>35.776699999999998</v>
       </c>
       <c r="J159">
-        <v>11.3589</v>
+        <v>140.31890000000001</v>
       </c>
       <c r="K159" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="L159" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
-        <v>42896</v>
+        <v>42889</v>
       </c>
       <c r="B160" s="4">
-        <v>42896</v>
+        <v>42889</v>
       </c>
       <c r="C160" t="s">
-        <v>579</v>
+        <v>576</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I160">
+        <v>44.509300000000003</v>
+      </c>
+      <c r="J160">
+        <v>11.3589</v>
+      </c>
+      <c r="K160" t="s">
+        <v>577</v>
       </c>
       <c r="L160" s="5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
-        <v>42966</v>
+        <v>42896</v>
       </c>
       <c r="B161" s="4">
-        <v>42967</v>
+        <v>42896</v>
       </c>
       <c r="C161" t="s">
-        <v>581</v>
-      </c>
-      <c r="D161" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" t="s">
-        <v>14</v>
-      </c>
-      <c r="F161" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G161" t="s">
-        <v>582</v>
-      </c>
-      <c r="H161" t="s">
-        <v>582</v>
-      </c>
-      <c r="I161">
-        <v>46.129600000000003</v>
-      </c>
-      <c r="J161">
-        <v>11.3514</v>
-      </c>
-      <c r="K161" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="L161" s="5" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
-        <v>42973</v>
+        <v>42966</v>
       </c>
       <c r="B162" s="4">
-        <v>42982</v>
+        <v>42967</v>
       </c>
       <c r="C162" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D162" t="s">
         <v>13</v>
@@ -9908,30 +9931,33 @@
         <v>1078</v>
       </c>
       <c r="G162" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="H162" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="I162">
-        <v>43.318800000000003</v>
+        <v>46.129600000000003</v>
       </c>
       <c r="J162">
-        <v>11.3308</v>
+        <v>11.3514</v>
+      </c>
+      <c r="K162" t="s">
+        <v>583</v>
       </c>
       <c r="L162" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
-        <v>43016</v>
+        <v>42973</v>
       </c>
       <c r="B163" s="4">
-        <v>43016</v>
+        <v>42982</v>
       </c>
       <c r="C163" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D163" t="s">
         <v>13</v>
@@ -9943,33 +9969,30 @@
         <v>1078</v>
       </c>
       <c r="G163" t="s">
-        <v>19</v>
+        <v>586</v>
       </c>
       <c r="H163" t="s">
-        <v>19</v>
+        <v>586</v>
       </c>
       <c r="I163">
-        <v>44.494900000000001</v>
+        <v>43.318800000000003</v>
       </c>
       <c r="J163">
-        <v>11.342599999999999</v>
-      </c>
-      <c r="K163" s="6" t="s">
-        <v>589</v>
+        <v>11.3308</v>
       </c>
       <c r="L163" s="5" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
-        <v>43022</v>
+        <v>43016</v>
       </c>
       <c r="B164" s="4">
-        <v>43036</v>
+        <v>43016</v>
       </c>
       <c r="C164" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D164" t="s">
         <v>13</v>
@@ -9981,206 +10004,212 @@
         <v>1078</v>
       </c>
       <c r="G164" t="s">
-        <v>592</v>
+        <v>19</v>
       </c>
       <c r="H164" t="s">
-        <v>592</v>
+        <v>19</v>
       </c>
       <c r="I164">
-        <v>44.262</v>
+        <v>44.494900000000001</v>
       </c>
       <c r="J164">
-        <v>12.3499</v>
-      </c>
-      <c r="K164" t="s">
-        <v>593</v>
+        <v>11.342599999999999</v>
+      </c>
+      <c r="K164" s="6" t="s">
+        <v>589</v>
       </c>
       <c r="L164" s="5" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
-        <v>43084</v>
+        <v>43022</v>
       </c>
       <c r="B165" s="4">
-        <v>43086</v>
+        <v>43036</v>
       </c>
       <c r="C165" t="s">
-        <v>595</v>
-      </c>
-      <c r="D165" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="D165" t="s">
         <v>13</v>
       </c>
-      <c r="E165" s="6" t="s">
+      <c r="E165" t="s">
         <v>14</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F165" t="s">
         <v>1078</v>
       </c>
-      <c r="G165" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H165" s="6" t="s">
-        <v>19</v>
+      <c r="G165" t="s">
+        <v>592</v>
+      </c>
+      <c r="H165" t="s">
+        <v>592</v>
       </c>
       <c r="I165">
-        <v>44.509300000000003</v>
+        <v>44.262</v>
       </c>
       <c r="J165">
-        <v>11.3589</v>
+        <v>12.3499</v>
       </c>
       <c r="K165" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="L165" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
-        <v>43148</v>
+        <v>43084</v>
       </c>
       <c r="B166" s="4">
-        <v>43148</v>
+        <v>43086</v>
       </c>
       <c r="C166" t="s">
-        <v>598</v>
-      </c>
-      <c r="D166" t="s">
+        <v>595</v>
+      </c>
+      <c r="D166" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F166" t="s">
+      <c r="F166" s="6" t="s">
         <v>1078</v>
       </c>
-      <c r="G166" t="s">
-        <v>598</v>
-      </c>
-      <c r="H166" t="s">
-        <v>598</v>
+      <c r="G166" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="I166">
-        <v>43.940600000000003</v>
+        <v>44.509300000000003</v>
       </c>
       <c r="J166">
-        <v>12.7722</v>
+        <v>11.3589</v>
       </c>
       <c r="K166" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L166" s="5" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="167" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
-        <v>43182</v>
+        <v>43148</v>
       </c>
       <c r="B167" s="4">
-        <v>43185</v>
+        <v>43148</v>
       </c>
       <c r="C167" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D167" t="s">
         <v>13</v>
       </c>
       <c r="E167" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F167" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G167" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="H167" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="I167">
-        <v>39.8628</v>
+        <v>43.940600000000003</v>
       </c>
       <c r="J167">
-        <v>-4.0273000000000003</v>
+        <v>12.7722</v>
       </c>
       <c r="K167" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="L167" s="5" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="168" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
-        <v>43198</v>
+        <v>43182</v>
       </c>
       <c r="B168" s="4">
-        <v>43198</v>
+        <v>43185</v>
       </c>
       <c r="C168" t="s">
-        <v>605</v>
-      </c>
-      <c r="D168" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="D168" t="s">
         <v>13</v>
       </c>
-      <c r="E168" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G168" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>19</v>
+      <c r="E168" t="s">
+        <v>38</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G168" t="s">
+        <v>602</v>
+      </c>
+      <c r="H168" t="s">
+        <v>602</v>
       </c>
       <c r="I168">
-        <v>44.509300000000003</v>
+        <v>39.8628</v>
       </c>
       <c r="J168">
-        <v>11.3589</v>
+        <v>-4.0273000000000003</v>
       </c>
       <c r="K168" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="L168" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
-        <v>43272</v>
+        <v>43198</v>
       </c>
       <c r="B169" s="4">
-        <v>43288</v>
+        <v>43198</v>
       </c>
       <c r="C169" t="s">
-        <v>608</v>
-      </c>
-      <c r="D169" t="s">
+        <v>605</v>
+      </c>
+      <c r="D169" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E169" t="s">
-        <v>27</v>
-      </c>
-      <c r="F169" t="s">
-        <v>1079</v>
+      <c r="E169" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G169" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H169" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="I169">
-        <v>55.378100000000003</v>
+        <v>44.509300000000003</v>
       </c>
       <c r="J169">
-        <v>-3.4359999999999999</v>
+        <v>11.3589</v>
       </c>
       <c r="K169" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="L169" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10191,7 +10220,7 @@
         <v>43288</v>
       </c>
       <c r="C170" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D170" t="s">
         <v>13</v>
@@ -10209,10 +10238,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K170" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="L170" s="5" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="171" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10220,10 +10249,10 @@
         <v>43272</v>
       </c>
       <c r="B171" s="4">
-        <v>43289</v>
+        <v>43288</v>
       </c>
       <c r="C171" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D171" t="s">
         <v>13</v>
@@ -10241,21 +10270,21 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K171" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="L171" s="5" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="172" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
-        <v>43273</v>
+        <v>43272</v>
       </c>
       <c r="B172" s="4">
-        <v>43285</v>
+        <v>43289</v>
       </c>
       <c r="C172" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D172" t="s">
         <v>13</v>
@@ -10273,10 +10302,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K172" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="L172" s="5" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="173" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10284,10 +10313,10 @@
         <v>43273</v>
       </c>
       <c r="B173" s="4">
-        <v>43286</v>
+        <v>43285</v>
       </c>
       <c r="C173" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -10305,10 +10334,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K173" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="L173" s="5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10316,10 +10345,10 @@
         <v>43273</v>
       </c>
       <c r="B174" s="4">
-        <v>43287</v>
+        <v>43286</v>
       </c>
       <c r="C174" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D174" t="s">
         <v>13</v>
@@ -10337,10 +10366,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K174" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="L174" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10348,10 +10377,10 @@
         <v>43273</v>
       </c>
       <c r="B175" s="4">
-        <v>43288</v>
+        <v>43287</v>
       </c>
       <c r="C175" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D175" t="s">
         <v>13</v>
@@ -10369,10 +10398,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K175" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="L175" s="5" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10383,7 +10412,7 @@
         <v>43288</v>
       </c>
       <c r="C176" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D176" t="s">
         <v>13</v>
@@ -10401,10 +10430,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K176" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L176" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10415,7 +10444,7 @@
         <v>43288</v>
       </c>
       <c r="C177" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D177" t="s">
         <v>13</v>
@@ -10433,10 +10462,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K177" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="L177" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="178" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10444,10 +10473,10 @@
         <v>43273</v>
       </c>
       <c r="B178" s="4">
-        <v>43289</v>
+        <v>43288</v>
       </c>
       <c r="C178" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D178" t="s">
         <v>13</v>
@@ -10465,21 +10494,21 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K178" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="L178" s="5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="179" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
-        <v>43275</v>
+        <v>43273</v>
       </c>
       <c r="B179" s="4">
-        <v>43285</v>
+        <v>43289</v>
       </c>
       <c r="C179" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D179" t="s">
         <v>13</v>
@@ -10497,10 +10526,10 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K179" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="L179" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="180" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10508,10 +10537,10 @@
         <v>43275</v>
       </c>
       <c r="B180" s="4">
-        <v>43288</v>
+        <v>43285</v>
       </c>
       <c r="C180" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D180" t="s">
         <v>13</v>
@@ -10528,19 +10557,22 @@
       <c r="J180">
         <v>-3.4359999999999999</v>
       </c>
+      <c r="K180" t="s">
+        <v>639</v>
+      </c>
       <c r="L180" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="181" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
-        <v>43279</v>
+        <v>43275</v>
       </c>
       <c r="B181" s="4">
-        <v>43287</v>
+        <v>43288</v>
       </c>
       <c r="C181" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D181" t="s">
         <v>13</v>
@@ -10557,22 +10589,19 @@
       <c r="J181">
         <v>-3.4359999999999999</v>
       </c>
-      <c r="K181" t="s">
-        <v>644</v>
-      </c>
       <c r="L181" s="5" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="182" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
-        <v>43282</v>
+        <v>43279</v>
       </c>
       <c r="B182" s="4">
-        <v>43286</v>
+        <v>43287</v>
       </c>
       <c r="C182" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D182" t="s">
         <v>13</v>
@@ -10590,21 +10619,21 @@
         <v>-3.4359999999999999</v>
       </c>
       <c r="K182" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="L182" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="183" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
-        <v>43287</v>
+        <v>43282</v>
       </c>
       <c r="B183" s="4">
-        <v>43288</v>
+        <v>43286</v>
       </c>
       <c r="C183" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D183" t="s">
         <v>13</v>
@@ -10615,138 +10644,132 @@
       <c r="F183" t="s">
         <v>1079</v>
       </c>
-      <c r="G183" t="s">
-        <v>650</v>
-      </c>
-      <c r="H183" t="s">
-        <v>650</v>
-      </c>
       <c r="I183">
-        <v>56.058</v>
+        <v>55.378100000000003</v>
       </c>
       <c r="J183">
-        <v>-2.7172999999999998</v>
+        <v>-3.4359999999999999</v>
       </c>
       <c r="K183" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="L183" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="184" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
-        <v>43370</v>
+        <v>43287</v>
       </c>
       <c r="B184" s="4">
-        <v>43373</v>
+        <v>43288</v>
       </c>
       <c r="C184" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D184" t="s">
         <v>13</v>
       </c>
       <c r="E184" t="s">
-        <v>654</v>
+        <v>27</v>
       </c>
       <c r="F184" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="G184" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="H184" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="I184">
-        <v>59.913899999999998</v>
+        <v>56.058</v>
       </c>
       <c r="J184">
-        <v>10.7522</v>
+        <v>-2.7172999999999998</v>
       </c>
       <c r="K184" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="L184" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="185" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
-        <v>43456</v>
+        <v>43370</v>
       </c>
       <c r="B185" s="4">
-        <v>43456</v>
+        <v>43373</v>
       </c>
       <c r="C185" t="s">
-        <v>658</v>
+        <v>653</v>
+      </c>
+      <c r="D185" t="s">
+        <v>13</v>
+      </c>
+      <c r="E185" t="s">
+        <v>654</v>
+      </c>
+      <c r="F185" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G185" t="s">
+        <v>655</v>
+      </c>
+      <c r="H185" t="s">
+        <v>655</v>
+      </c>
+      <c r="I185">
+        <v>59.913899999999998</v>
+      </c>
+      <c r="J185">
+        <v>10.7522</v>
+      </c>
+      <c r="K185" t="s">
+        <v>656</v>
       </c>
       <c r="L185" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
-        <v>43505</v>
+        <v>43456</v>
       </c>
       <c r="B186" s="4">
-        <v>43505</v>
+        <v>43456</v>
       </c>
       <c r="C186" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L186" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="187" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
-        <v>43536</v>
+        <v>43505</v>
       </c>
       <c r="B187" s="4">
-        <v>43536</v>
+        <v>43505</v>
       </c>
       <c r="C187" t="s">
-        <v>662</v>
-      </c>
-      <c r="D187" t="s">
-        <v>164</v>
-      </c>
-      <c r="E187" t="s">
-        <v>663</v>
-      </c>
-      <c r="F187" t="s">
-        <v>663</v>
-      </c>
-      <c r="G187" t="s">
-        <v>664</v>
-      </c>
-      <c r="H187" t="s">
-        <v>664</v>
-      </c>
-      <c r="I187">
-        <v>25.033000000000001</v>
-      </c>
-      <c r="J187">
-        <v>121.5654</v>
-      </c>
-      <c r="K187" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="L187" s="5" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="188" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
-        <v>43537</v>
+        <v>43536</v>
       </c>
       <c r="B188" s="4">
-        <v>43538</v>
+        <v>43536</v>
       </c>
       <c r="C188" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="D188" t="s">
         <v>164</v>
@@ -10770,21 +10793,21 @@
         <v>121.5654</v>
       </c>
       <c r="K188" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="L188" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="189" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
-        <v>43538</v>
+        <v>43537</v>
       </c>
       <c r="B189" s="4">
         <v>43538</v>
       </c>
       <c r="C189" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D189" t="s">
         <v>164</v>
@@ -10808,21 +10831,21 @@
         <v>121.5654</v>
       </c>
       <c r="K189" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="L189" s="5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="190" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
-        <v>43539</v>
+        <v>43538</v>
       </c>
       <c r="B190" s="4">
-        <v>43539</v>
+        <v>43538</v>
       </c>
       <c r="C190" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D190" t="s">
         <v>164</v>
@@ -10840,16 +10863,16 @@
         <v>664</v>
       </c>
       <c r="I190">
-        <v>25.1096</v>
+        <v>25.033000000000001</v>
       </c>
       <c r="J190">
-        <v>121.84520000000001</v>
+        <v>121.5654</v>
       </c>
       <c r="K190" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="L190" s="5" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="191" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -10860,7 +10883,7 @@
         <v>43539</v>
       </c>
       <c r="C191" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D191" t="s">
         <v>164</v>
@@ -10878,27 +10901,27 @@
         <v>664</v>
       </c>
       <c r="I191">
-        <v>25.033000000000001</v>
+        <v>25.1096</v>
       </c>
       <c r="J191">
-        <v>121.5654</v>
+        <v>121.84520000000001</v>
       </c>
       <c r="K191" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="L191" s="5" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="192" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
-        <v>43540</v>
+        <v>43539</v>
       </c>
       <c r="B192" s="4">
-        <v>43540</v>
+        <v>43539</v>
       </c>
       <c r="C192" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D192" t="s">
         <v>164</v>
@@ -10922,21 +10945,21 @@
         <v>121.5654</v>
       </c>
       <c r="K192" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="L192" s="5" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="193" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
-        <v>43541</v>
+        <v>43540</v>
       </c>
       <c r="B193" s="4">
-        <v>43543</v>
+        <v>43540</v>
       </c>
       <c r="C193" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D193" t="s">
         <v>164</v>
@@ -10948,33 +10971,33 @@
         <v>663</v>
       </c>
       <c r="G193" t="s">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="H193" t="s">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="I193">
-        <v>24.1477</v>
+        <v>25.033000000000001</v>
       </c>
       <c r="J193">
-        <v>120.67359999999999</v>
+        <v>121.5654</v>
       </c>
       <c r="K193" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="L193" s="5" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="194" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
-        <v>43542</v>
+        <v>43541</v>
       </c>
       <c r="B194" s="4">
         <v>43543</v>
       </c>
       <c r="C194" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D194" t="s">
         <v>164</v>
@@ -10986,33 +11009,33 @@
         <v>663</v>
       </c>
       <c r="G194" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="H194" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="I194">
-        <v>24.056000000000001</v>
+        <v>24.1477</v>
       </c>
       <c r="J194">
-        <v>120.435</v>
+        <v>120.67359999999999</v>
       </c>
       <c r="K194" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="L194" s="5" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="195" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
-        <v>43545</v>
+        <v>43542</v>
       </c>
       <c r="B195" s="4">
-        <v>43545</v>
+        <v>43543</v>
       </c>
       <c r="C195" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D195" t="s">
         <v>164</v>
@@ -11024,33 +11047,33 @@
         <v>663</v>
       </c>
       <c r="G195" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="H195" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="I195">
-        <v>22.9999</v>
+        <v>24.056000000000001</v>
       </c>
       <c r="J195">
-        <v>120.2269</v>
+        <v>120.435</v>
       </c>
       <c r="K195" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="L195" s="5" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="196" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
-        <v>43546</v>
+        <v>43545</v>
       </c>
       <c r="B196" s="4">
-        <v>43546</v>
+        <v>43545</v>
       </c>
       <c r="C196" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D196" t="s">
         <v>164</v>
@@ -11071,24 +11094,24 @@
         <v>22.9999</v>
       </c>
       <c r="J196">
-        <v>120.16679999999999</v>
+        <v>120.2269</v>
       </c>
       <c r="K196" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="L196" s="5" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="197" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
-        <v>43547</v>
+        <v>43546</v>
       </c>
       <c r="B197" s="4">
-        <v>43547</v>
+        <v>43546</v>
       </c>
       <c r="C197" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D197" t="s">
         <v>164</v>
@@ -11100,71 +11123,71 @@
         <v>663</v>
       </c>
       <c r="G197" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="H197" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="I197">
-        <v>22.627300000000002</v>
+        <v>22.9999</v>
       </c>
       <c r="J197">
-        <v>120.3014</v>
+        <v>120.16679999999999</v>
       </c>
       <c r="K197" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="L197" s="5" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="198" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
-        <v>43548</v>
+        <v>43547</v>
       </c>
       <c r="B198" s="4">
-        <v>43549</v>
+        <v>43547</v>
       </c>
       <c r="C198" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D198" t="s">
         <v>164</v>
       </c>
       <c r="E198" t="s">
-        <v>244</v>
+        <v>663</v>
       </c>
       <c r="F198" t="s">
-        <v>1088</v>
+        <v>663</v>
       </c>
       <c r="G198" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="H198" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="I198">
-        <v>22.319299999999998</v>
+        <v>22.627300000000002</v>
       </c>
       <c r="J198">
-        <v>114.1694</v>
+        <v>120.3014</v>
       </c>
       <c r="K198" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="L198" s="5" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="199" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
-        <v>43549</v>
+        <v>43548</v>
       </c>
       <c r="B199" s="4">
         <v>43549</v>
       </c>
       <c r="C199" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D199" t="s">
         <v>164</v>
@@ -11188,10 +11211,10 @@
         <v>114.1694</v>
       </c>
       <c r="K199" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="L199" s="5" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="200" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -11202,7 +11225,7 @@
         <v>43549</v>
       </c>
       <c r="C200" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D200" t="s">
         <v>164</v>
@@ -11226,21 +11249,21 @@
         <v>114.1694</v>
       </c>
       <c r="K200" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="L200" s="5" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="201" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
-        <v>43550</v>
+        <v>43549</v>
       </c>
       <c r="B201" s="4">
-        <v>43550</v>
+        <v>43549</v>
       </c>
       <c r="C201" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D201" t="s">
         <v>164</v>
@@ -11264,21 +11287,21 @@
         <v>114.1694</v>
       </c>
       <c r="K201" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="L201" s="5" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
-        <v>43551</v>
+        <v>43550</v>
       </c>
       <c r="B202" s="4">
-        <v>43551</v>
+        <v>43550</v>
       </c>
       <c r="C202" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D202" t="s">
         <v>164</v>
@@ -11290,33 +11313,33 @@
         <v>1088</v>
       </c>
       <c r="G202" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="H202" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="I202">
-        <v>22.198699999999999</v>
+        <v>22.319299999999998</v>
       </c>
       <c r="J202">
-        <v>113.54389999999999</v>
+        <v>114.1694</v>
       </c>
       <c r="K202" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="L202" s="5" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="203" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
-        <v>43552</v>
+        <v>43551</v>
       </c>
       <c r="B203" s="4">
-        <v>43552</v>
+        <v>43551</v>
       </c>
       <c r="C203" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D203" t="s">
         <v>164</v>
@@ -11328,33 +11351,33 @@
         <v>1088</v>
       </c>
       <c r="G203" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="H203" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="I203">
-        <v>22.319299999999998</v>
+        <v>22.198699999999999</v>
       </c>
       <c r="J203">
-        <v>114.1694</v>
+        <v>113.54389999999999</v>
       </c>
       <c r="K203" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="L203" s="5" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="204" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
-        <v>43553</v>
+        <v>43552</v>
       </c>
       <c r="B204" s="4">
-        <v>43553</v>
+        <v>43552</v>
       </c>
       <c r="C204" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D204" t="s">
         <v>164</v>
@@ -11378,59 +11401,59 @@
         <v>114.1694</v>
       </c>
       <c r="K204" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="L204" s="5" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="205" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
-        <v>43653</v>
+        <v>43553</v>
       </c>
       <c r="B205" s="4">
-        <v>43757</v>
+        <v>43553</v>
       </c>
       <c r="C205" t="s">
-        <v>724</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E205" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F205" s="6" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G205" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H205" s="6" t="s">
-        <v>19</v>
+        <v>721</v>
+      </c>
+      <c r="D205" t="s">
+        <v>164</v>
+      </c>
+      <c r="E205" t="s">
+        <v>244</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G205" t="s">
+        <v>702</v>
+      </c>
+      <c r="H205" t="s">
+        <v>702</v>
       </c>
       <c r="I205">
-        <v>44.509300000000003</v>
+        <v>22.319299999999998</v>
       </c>
       <c r="J205">
-        <v>11.3589</v>
+        <v>114.1694</v>
       </c>
       <c r="K205" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="L205" s="5" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="206" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
-        <v>43673</v>
+        <v>43653</v>
       </c>
       <c r="B206" s="4">
-        <v>43693</v>
+        <v>43757</v>
       </c>
       <c r="C206" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>13</v>
@@ -11454,21 +11477,21 @@
         <v>11.3589</v>
       </c>
       <c r="K206" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="L206" s="5" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="207" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
-        <v>43682</v>
+        <v>43673</v>
       </c>
       <c r="B207" s="4">
-        <v>43871</v>
+        <v>43693</v>
       </c>
       <c r="C207" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D207" s="6" t="s">
         <v>13</v>
@@ -11492,48 +11515,48 @@
         <v>11.3589</v>
       </c>
       <c r="K207" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="L207" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="208" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
-        <v>43723</v>
+        <v>43682</v>
       </c>
       <c r="B208" s="4">
-        <v>43723</v>
+        <v>43871</v>
       </c>
       <c r="C208" t="s">
-        <v>733</v>
-      </c>
-      <c r="D208" t="s">
+        <v>730</v>
+      </c>
+      <c r="D208" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E208" t="s">
-        <v>734</v>
-      </c>
-      <c r="F208" t="s">
-        <v>1094</v>
-      </c>
-      <c r="G208" t="s">
-        <v>735</v>
-      </c>
-      <c r="H208" t="s">
-        <v>735</v>
+      <c r="E208" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H208" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="I208">
-        <v>47.050199999999997</v>
+        <v>44.509300000000003</v>
       </c>
       <c r="J208">
-        <v>8.3093000000000004</v>
+        <v>11.3589</v>
       </c>
       <c r="K208" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="L208" s="5" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
     </row>
     <row r="209" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -11541,10 +11564,10 @@
         <v>43723</v>
       </c>
       <c r="B209" s="4">
-        <v>43724</v>
+        <v>43723</v>
       </c>
       <c r="C209" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="D209" t="s">
         <v>13</v>
@@ -11556,60 +11579,60 @@
         <v>1094</v>
       </c>
       <c r="G209" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="H209" t="s">
-        <v>1095</v>
+        <v>735</v>
       </c>
       <c r="I209">
-        <v>47.559600000000003</v>
+        <v>47.050199999999997</v>
       </c>
       <c r="J209">
-        <v>7.5885999999999996</v>
+        <v>8.3093000000000004</v>
       </c>
       <c r="K209" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="L209" s="5" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="210" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
-        <v>43724</v>
+        <v>43723</v>
       </c>
       <c r="B210" s="4">
         <v>43724</v>
       </c>
       <c r="C210" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D210" t="s">
         <v>13</v>
       </c>
       <c r="E210" t="s">
-        <v>102</v>
+        <v>734</v>
       </c>
       <c r="F210" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="G210" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="H210" t="s">
-        <v>743</v>
+        <v>1095</v>
       </c>
       <c r="I210">
-        <v>48.0794</v>
+        <v>47.559600000000003</v>
       </c>
       <c r="J210">
-        <v>7.3585000000000003</v>
+        <v>7.5885999999999996</v>
       </c>
       <c r="K210" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="L210" s="5" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="211" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -11620,77 +11643,83 @@
         <v>43724</v>
       </c>
       <c r="C211" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D211" t="s">
         <v>13</v>
       </c>
       <c r="E211" t="s">
-        <v>747</v>
+        <v>102</v>
       </c>
       <c r="F211" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="G211" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="H211" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="I211">
-        <v>47.593400000000003</v>
+        <v>48.0794</v>
       </c>
       <c r="J211">
-        <v>7.6200999999999999</v>
+        <v>7.3585000000000003</v>
       </c>
       <c r="K211" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="L211" s="5" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="212" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
-        <v>43725</v>
+        <v>43724</v>
       </c>
       <c r="B212" s="4">
-        <v>43750</v>
+        <v>43724</v>
       </c>
       <c r="C212" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="D212" t="s">
         <v>13</v>
       </c>
       <c r="E212" t="s">
-        <v>102</v>
+        <v>747</v>
       </c>
       <c r="F212" t="s">
-        <v>1084</v>
+        <v>1096</v>
+      </c>
+      <c r="G212" t="s">
+        <v>748</v>
+      </c>
+      <c r="H212" t="s">
+        <v>748</v>
       </c>
       <c r="I212">
-        <v>48.489699999999999</v>
+        <v>47.593400000000003</v>
       </c>
       <c r="J212">
-        <v>7.5334000000000003</v>
+        <v>7.6200999999999999</v>
       </c>
       <c r="K212" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="L212" s="5" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="213" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
-        <v>43727</v>
+        <v>43725</v>
       </c>
       <c r="B213" s="4">
-        <v>43727</v>
+        <v>43750</v>
       </c>
       <c r="C213" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D213" t="s">
         <v>13</v>
@@ -11701,124 +11730,118 @@
       <c r="F213" t="s">
         <v>1084</v>
       </c>
-      <c r="G213" t="s">
-        <v>755</v>
-      </c>
-      <c r="H213" t="s">
-        <v>1097</v>
-      </c>
       <c r="I213">
-        <v>48.573399999999999</v>
+        <v>48.489699999999999</v>
       </c>
       <c r="J213">
-        <v>7.7521000000000004</v>
+        <v>7.5334000000000003</v>
       </c>
       <c r="K213" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="L213" s="5" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="214" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
-        <v>43728</v>
+        <v>43727</v>
       </c>
       <c r="B214" s="4">
-        <v>43728</v>
+        <v>43727</v>
       </c>
       <c r="C214" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D214" t="s">
         <v>13</v>
       </c>
       <c r="E214" t="s">
-        <v>734</v>
+        <v>102</v>
       </c>
       <c r="F214" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="G214" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="H214" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="I214">
-        <v>47.376899999999999</v>
+        <v>48.573399999999999</v>
       </c>
       <c r="J214">
-        <v>8.5417000000000005</v>
+        <v>7.7521000000000004</v>
       </c>
       <c r="K214" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="L214" s="5" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="215" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
-        <v>43748</v>
+        <v>43728</v>
       </c>
       <c r="B215" s="4">
-        <v>44711</v>
+        <v>43728</v>
       </c>
       <c r="C215" t="s">
-        <v>762</v>
+        <v>758</v>
+      </c>
+      <c r="D215" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" t="s">
+        <v>734</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G215" t="s">
+        <v>759</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I215">
+        <v>47.376899999999999</v>
+      </c>
+      <c r="J215">
+        <v>8.5417000000000005</v>
+      </c>
+      <c r="K215" t="s">
+        <v>760</v>
       </c>
       <c r="L215" s="5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="216" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
-        <v>43973</v>
+        <v>43748</v>
       </c>
       <c r="B216" s="4">
-        <v>43973</v>
+        <v>44711</v>
       </c>
       <c r="C216" t="s">
-        <v>764</v>
-      </c>
-      <c r="D216" t="s">
-        <v>13</v>
-      </c>
-      <c r="E216" t="s">
-        <v>14</v>
-      </c>
-      <c r="F216" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G216" s="6" t="s">
-        <v>765</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>765</v>
-      </c>
-      <c r="I216">
-        <v>44.659500000000001</v>
-      </c>
-      <c r="J216">
-        <v>12.251099999999999</v>
-      </c>
-      <c r="K216" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="L216" s="5" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="217" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
-        <v>43988</v>
+        <v>43973</v>
       </c>
       <c r="B217" s="4">
-        <v>43993</v>
+        <v>43973</v>
       </c>
       <c r="C217" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="D217" t="s">
         <v>13</v>
@@ -11829,34 +11852,34 @@
       <c r="F217" t="s">
         <v>1078</v>
       </c>
-      <c r="G217" t="s">
-        <v>769</v>
-      </c>
-      <c r="H217" t="s">
-        <v>769</v>
+      <c r="G217" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="H217" s="6" t="s">
+        <v>765</v>
       </c>
       <c r="I217">
-        <v>46.671300000000002</v>
+        <v>44.659500000000001</v>
       </c>
       <c r="J217">
-        <v>11.1594</v>
+        <v>12.251099999999999</v>
       </c>
       <c r="K217" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="L217" s="5" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="218" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
-        <v>44008</v>
+        <v>43988</v>
       </c>
       <c r="B218" s="4">
-        <v>44008</v>
+        <v>43993</v>
       </c>
       <c r="C218" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D218" t="s">
         <v>13</v>
@@ -11868,97 +11891,109 @@
         <v>1078</v>
       </c>
       <c r="G218" t="s">
-        <v>415</v>
+        <v>769</v>
       </c>
       <c r="H218" t="s">
-        <v>415</v>
+        <v>769</v>
       </c>
       <c r="I218">
-        <v>44.801499999999997</v>
+        <v>46.671300000000002</v>
       </c>
       <c r="J218">
-        <v>10.3279</v>
+        <v>11.1594</v>
       </c>
       <c r="K218" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="L218" s="5" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="219" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
-        <v>44086</v>
+        <v>44008</v>
       </c>
       <c r="B219" s="4">
-        <v>44101</v>
+        <v>44008</v>
       </c>
       <c r="C219" t="s">
-        <v>775</v>
-      </c>
-      <c r="D219" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="D219" t="s">
         <v>13</v>
       </c>
-      <c r="E219" s="6" t="s">
+      <c r="E219" t="s">
         <v>14</v>
       </c>
-      <c r="F219" s="6" t="s">
+      <c r="F219" t="s">
         <v>1078</v>
       </c>
-      <c r="G219" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H219" s="6" t="s">
-        <v>19</v>
+      <c r="G219" t="s">
+        <v>415</v>
+      </c>
+      <c r="H219" t="s">
+        <v>415</v>
       </c>
       <c r="I219">
-        <v>44.509300000000003</v>
+        <v>44.801499999999997</v>
       </c>
       <c r="J219">
-        <v>11.3589</v>
+        <v>10.3279</v>
       </c>
       <c r="K219" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="L219" s="5" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="220" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
-        <v>44110</v>
+        <v>44086</v>
       </c>
       <c r="B220" s="4">
-        <v>44114</v>
+        <v>44101</v>
       </c>
       <c r="C220" t="s">
-        <v>778</v>
-      </c>
-      <c r="D220" t="s">
+        <v>775</v>
+      </c>
+      <c r="D220" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E220" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F220" t="s">
+      <c r="F220" s="6" t="s">
         <v>1078</v>
       </c>
+      <c r="G220" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H220" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I220">
+        <v>44.509300000000003</v>
+      </c>
+      <c r="J220">
+        <v>11.3589</v>
+      </c>
       <c r="K220" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="L220" s="5" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="221" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
-        <v>44117</v>
+        <v>44110</v>
       </c>
       <c r="B221" s="4">
-        <v>44117</v>
+        <v>44114</v>
       </c>
       <c r="C221" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D221" t="s">
         <v>13</v>
@@ -11969,34 +12004,28 @@
       <c r="F221" t="s">
         <v>1078</v>
       </c>
-      <c r="G221" t="s">
-        <v>781</v>
-      </c>
-      <c r="H221" t="s">
-        <v>1099</v>
-      </c>
       <c r="I221">
-        <v>45.440800000000003</v>
+        <v>43.567599999999999</v>
       </c>
       <c r="J221">
-        <v>12.3155</v>
+        <v>12.583</v>
       </c>
       <c r="K221" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="L221" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="222" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
-        <v>44135</v>
+        <v>44117</v>
       </c>
       <c r="B222" s="4">
-        <v>44135</v>
+        <v>44117</v>
       </c>
       <c r="C222" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D222" t="s">
         <v>13</v>
@@ -12008,85 +12037,85 @@
         <v>1078</v>
       </c>
       <c r="G222" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H222" t="s">
-        <v>785</v>
+        <v>1099</v>
       </c>
       <c r="I222">
-        <v>43.896900000000002</v>
+        <v>45.440800000000003</v>
       </c>
       <c r="J222">
-        <v>12.343400000000001</v>
-      </c>
-      <c r="K222" s="6" t="s">
-        <v>786</v>
+        <v>12.3155</v>
+      </c>
+      <c r="K222" t="s">
+        <v>782</v>
       </c>
       <c r="L222" s="5" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="223" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
-        <v>44142</v>
+        <v>44135</v>
       </c>
       <c r="B223" s="4">
-        <v>44142</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>788</v>
+        <v>44135</v>
+      </c>
+      <c r="C223" t="s">
+        <v>784</v>
+      </c>
+      <c r="D223" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" t="s">
+        <v>14</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G223" t="s">
+        <v>785</v>
+      </c>
+      <c r="H223" t="s">
+        <v>785</v>
+      </c>
+      <c r="I223">
+        <v>43.896900000000002</v>
+      </c>
+      <c r="J223">
+        <v>12.343400000000001</v>
+      </c>
+      <c r="K223" s="6" t="s">
+        <v>786</v>
       </c>
       <c r="L223" s="5" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="224" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
-        <v>44346</v>
+        <v>44142</v>
       </c>
       <c r="B224" s="4">
-        <v>44346</v>
+        <v>44142</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>790</v>
-      </c>
-      <c r="D224" t="s">
-        <v>13</v>
-      </c>
-      <c r="E224" t="s">
-        <v>14</v>
-      </c>
-      <c r="F224" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G224" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="I224">
-        <v>44.5745</v>
-      </c>
-      <c r="J224">
-        <v>11.7935</v>
-      </c>
-      <c r="K224" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="L224" s="5" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="225" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
-        <v>44361</v>
+        <v>44346</v>
       </c>
       <c r="B225" s="4">
-        <v>44361</v>
-      </c>
-      <c r="C225" t="s">
-        <v>794</v>
+        <v>44346</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>790</v>
       </c>
       <c r="D225" t="s">
         <v>13</v>
@@ -12098,33 +12127,33 @@
         <v>1078</v>
       </c>
       <c r="G225" s="6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="H225" s="6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="I225">
-        <v>45.279000000000003</v>
+        <v>44.5745</v>
       </c>
       <c r="J225">
-        <v>11.7296</v>
+        <v>11.7935</v>
       </c>
       <c r="K225" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="L225" s="5" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="226" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
-        <v>44373</v>
+        <v>44361</v>
       </c>
       <c r="B226" s="4">
-        <v>44375</v>
+        <v>44361</v>
       </c>
       <c r="C226" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D226" t="s">
         <v>13</v>
@@ -12135,34 +12164,34 @@
       <c r="F226" t="s">
         <v>1078</v>
       </c>
-      <c r="G226" t="s">
-        <v>799</v>
-      </c>
-      <c r="H226" t="s">
-        <v>799</v>
+      <c r="G226" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="H226" s="6" t="s">
+        <v>795</v>
       </c>
       <c r="I226">
-        <v>46.434699999999999</v>
+        <v>45.279000000000003</v>
       </c>
       <c r="J226">
-        <v>11.976699999999999</v>
+        <v>11.7296</v>
       </c>
       <c r="K226" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="L226" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="227" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
-        <v>44445</v>
+        <v>44373</v>
       </c>
       <c r="B227" s="4">
-        <v>44450</v>
+        <v>44375</v>
       </c>
       <c r="C227" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D227" t="s">
         <v>13</v>
@@ -12173,126 +12202,132 @@
       <c r="F227" t="s">
         <v>1078</v>
       </c>
+      <c r="G227" t="s">
+        <v>799</v>
+      </c>
+      <c r="H227" t="s">
+        <v>799</v>
+      </c>
+      <c r="I227">
+        <v>46.434699999999999</v>
+      </c>
+      <c r="J227">
+        <v>11.976699999999999</v>
+      </c>
       <c r="K227" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="L227" s="5" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="228" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
-        <v>44465</v>
+        <v>44445</v>
       </c>
       <c r="B228" s="4">
-        <v>44465</v>
+        <v>44450</v>
       </c>
       <c r="C228" t="s">
-        <v>805</v>
+        <v>802</v>
+      </c>
+      <c r="D228" t="s">
+        <v>13</v>
+      </c>
+      <c r="E228" t="s">
+        <v>14</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I228">
+        <v>45.998899999999999</v>
+      </c>
+      <c r="J228">
+        <v>9.2612000000000005</v>
+      </c>
+      <c r="K228" t="s">
+        <v>803</v>
       </c>
       <c r="L228" s="5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="229" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
-        <v>44527</v>
+        <v>44465</v>
       </c>
       <c r="B229" s="4">
-        <v>44527</v>
+        <v>44465</v>
       </c>
       <c r="C229" t="s">
-        <v>807</v>
-      </c>
-      <c r="D229" t="s">
-        <v>13</v>
-      </c>
-      <c r="E229" t="s">
-        <v>14</v>
-      </c>
-      <c r="F229" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G229" t="s">
-        <v>808</v>
-      </c>
-      <c r="H229" t="s">
-        <v>808</v>
-      </c>
-      <c r="I229">
-        <v>44.831400000000002</v>
-      </c>
-      <c r="J229">
-        <v>12.1107</v>
-      </c>
-      <c r="K229" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="L229" s="5" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
-        <v>44715</v>
+        <v>44527</v>
       </c>
       <c r="B230" s="4">
-        <v>44957</v>
+        <v>44527</v>
       </c>
       <c r="C230" t="s">
-        <v>811</v>
+        <v>807</v>
+      </c>
+      <c r="D230" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" t="s">
+        <v>14</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G230" t="s">
+        <v>808</v>
+      </c>
+      <c r="H230" t="s">
+        <v>808</v>
+      </c>
+      <c r="I230">
+        <v>44.831400000000002</v>
+      </c>
+      <c r="J230">
+        <v>12.1107</v>
+      </c>
+      <c r="K230" t="s">
+        <v>809</v>
       </c>
       <c r="L230" s="5" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="231" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
-        <v>44727</v>
+        <v>44715</v>
       </c>
       <c r="B231" s="4">
-        <v>44741</v>
+        <v>44957</v>
       </c>
       <c r="C231" t="s">
-        <v>813</v>
-      </c>
-      <c r="D231" t="s">
-        <v>13</v>
-      </c>
-      <c r="E231" t="s">
-        <v>102</v>
-      </c>
-      <c r="F231" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G231" t="s">
-        <v>814</v>
-      </c>
-      <c r="H231" t="s">
-        <v>814</v>
-      </c>
-      <c r="I231">
-        <v>44.652299999999997</v>
-      </c>
-      <c r="J231">
-        <v>-1.1785000000000001</v>
-      </c>
-      <c r="K231" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="L231" s="5" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="232" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
-        <v>44737</v>
+        <v>44727</v>
       </c>
       <c r="B232" s="4">
-        <v>44739</v>
+        <v>44741</v>
       </c>
       <c r="C232" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="D232" t="s">
         <v>13</v>
@@ -12304,33 +12339,33 @@
         <v>1084</v>
       </c>
       <c r="G232" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="H232" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="I232">
-        <v>45.188499999999998</v>
+        <v>44.652299999999997</v>
       </c>
       <c r="J232">
-        <v>5.7244999999999999</v>
+        <v>-1.1785000000000001</v>
       </c>
       <c r="K232" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="L232" s="5" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="233" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
-        <v>44740</v>
+        <v>44737</v>
       </c>
       <c r="B233" s="4">
-        <v>44740</v>
+        <v>44739</v>
       </c>
       <c r="C233" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D233" t="s">
         <v>13</v>
@@ -12342,33 +12377,33 @@
         <v>1084</v>
       </c>
       <c r="G233" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="H233" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="I233">
-        <v>46.160299999999999</v>
+        <v>45.188499999999998</v>
       </c>
       <c r="J233">
-        <v>-1.1511</v>
+        <v>5.7244999999999999</v>
       </c>
       <c r="K233" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="L233" s="5" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="234" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
-        <v>44741</v>
+        <v>44740</v>
       </c>
       <c r="B234" s="4">
-        <v>44742</v>
+        <v>44740</v>
       </c>
       <c r="C234" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D234" t="s">
         <v>13</v>
@@ -12380,33 +12415,33 @@
         <v>1084</v>
       </c>
       <c r="G234" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="H234" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="I234">
-        <v>44.837800000000001</v>
+        <v>46.160299999999999</v>
       </c>
       <c r="J234">
-        <v>-0.57920000000000005</v>
+        <v>-1.1511</v>
       </c>
       <c r="K234" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="L234" s="5" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="235" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
-        <v>44743</v>
+        <v>44741</v>
       </c>
       <c r="B235" s="4">
-        <v>44743</v>
+        <v>44742</v>
       </c>
       <c r="C235" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D235" t="s">
         <v>13</v>
@@ -12418,33 +12453,33 @@
         <v>1084</v>
       </c>
       <c r="G235" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="H235" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I235">
-        <v>44.633299999999998</v>
+        <v>44.837800000000001</v>
       </c>
       <c r="J235">
-        <v>-1.145</v>
+        <v>-0.57920000000000005</v>
       </c>
       <c r="K235" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="L235" s="5" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="236" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
-        <v>44744</v>
+        <v>44743</v>
       </c>
       <c r="B236" s="4">
-        <v>44744</v>
+        <v>44743</v>
       </c>
       <c r="C236" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="D236" t="s">
         <v>13</v>
@@ -12456,71 +12491,71 @@
         <v>1084</v>
       </c>
       <c r="G236" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H236" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="I236">
-        <v>43.483199999999997</v>
+        <v>44.633299999999998</v>
       </c>
       <c r="J236">
-        <v>-1.5586</v>
+        <v>-1.145</v>
       </c>
       <c r="K236" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="L236" s="5" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="237" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
-        <v>44745</v>
+        <v>44744</v>
       </c>
       <c r="B237" s="4">
-        <v>44745</v>
+        <v>44744</v>
       </c>
       <c r="C237" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="D237" t="s">
         <v>13</v>
       </c>
       <c r="E237" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="F237" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="G237" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="H237" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="I237">
-        <v>43.318300000000001</v>
+        <v>43.483199999999997</v>
       </c>
       <c r="J237">
-        <v>-1.9812000000000001</v>
+        <v>-1.5586</v>
       </c>
       <c r="K237" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="L237" s="5" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="238" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
-        <v>44746</v>
+        <v>44745</v>
       </c>
       <c r="B238" s="4">
-        <v>44746</v>
+        <v>44745</v>
       </c>
       <c r="C238" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="D238" t="s">
         <v>13</v>
@@ -12532,71 +12567,71 @@
         <v>1081</v>
       </c>
       <c r="G238" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="H238" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="I238">
-        <v>43.262999999999998</v>
+        <v>43.318300000000001</v>
       </c>
       <c r="J238">
-        <v>-2.9350000000000001</v>
+        <v>-1.9812000000000001</v>
       </c>
       <c r="K238" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="L238" s="5" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="239" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
-        <v>44747</v>
+        <v>44746</v>
       </c>
       <c r="B239" s="4">
-        <v>44748</v>
+        <v>44746</v>
       </c>
       <c r="C239" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="D239" t="s">
         <v>13</v>
       </c>
       <c r="E239" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="F239" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="G239" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="H239" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="I239">
-        <v>43.213000000000001</v>
+        <v>43.262999999999998</v>
       </c>
       <c r="J239">
-        <v>2.3491</v>
+        <v>-2.9350000000000001</v>
       </c>
       <c r="K239" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="L239" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
     </row>
     <row r="240" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
-        <v>44749</v>
+        <v>44747</v>
       </c>
       <c r="B240" s="4">
-        <v>44749</v>
+        <v>44748</v>
       </c>
       <c r="C240" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D240" t="s">
         <v>13</v>
@@ -12608,137 +12643,137 @@
         <v>1084</v>
       </c>
       <c r="G240" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="H240" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="I240">
-        <v>43.902299999999997</v>
+        <v>43.213000000000001</v>
       </c>
       <c r="J240">
-        <v>5.2925000000000004</v>
+        <v>2.3491</v>
       </c>
       <c r="K240" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="L240" s="5" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="241" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
-        <v>44825</v>
+        <v>44749</v>
       </c>
       <c r="B241" s="4">
-        <v>45192</v>
+        <v>44749</v>
       </c>
       <c r="C241" t="s">
-        <v>852</v>
+        <v>848</v>
+      </c>
+      <c r="D241" t="s">
+        <v>13</v>
+      </c>
+      <c r="E241" t="s">
+        <v>102</v>
+      </c>
+      <c r="F241" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G241" t="s">
+        <v>849</v>
+      </c>
+      <c r="H241" t="s">
+        <v>849</v>
+      </c>
+      <c r="I241">
+        <v>43.902299999999997</v>
+      </c>
+      <c r="J241">
+        <v>5.2925000000000004</v>
+      </c>
+      <c r="K241" t="s">
+        <v>850</v>
       </c>
       <c r="L241" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="242" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
-        <v>44996</v>
+        <v>44825</v>
       </c>
       <c r="B242" s="4">
-        <v>45120</v>
+        <v>45192</v>
       </c>
       <c r="C242" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="L242" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="243" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
-        <v>45039</v>
+        <v>44996</v>
       </c>
       <c r="B243" s="4">
-        <v>45039</v>
+        <v>45120</v>
       </c>
       <c r="C243" t="s">
-        <v>856</v>
-      </c>
-      <c r="D243" t="s">
-        <v>13</v>
-      </c>
-      <c r="E243" t="s">
-        <v>14</v>
-      </c>
-      <c r="F243" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G243" t="s">
-        <v>592</v>
-      </c>
-      <c r="H243" t="s">
-        <v>592</v>
-      </c>
-      <c r="I243">
-        <v>44.262</v>
-      </c>
-      <c r="J243">
-        <v>12.3499</v>
-      </c>
-      <c r="K243" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="L243" s="5" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="244" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
-        <v>45051</v>
+        <v>45039</v>
       </c>
       <c r="B244" s="4">
-        <v>45051</v>
+        <v>45039</v>
       </c>
       <c r="C244" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D244" t="s">
         <v>13</v>
       </c>
       <c r="E244" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F244" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G244" t="s">
-        <v>860</v>
+        <v>592</v>
       </c>
       <c r="H244" t="s">
-        <v>860</v>
+        <v>592</v>
       </c>
       <c r="I244">
-        <v>36.721299999999999</v>
+        <v>44.262</v>
       </c>
       <c r="J244">
-        <v>-4.4214000000000002</v>
-      </c>
-      <c r="K244" s="6" t="s">
-        <v>861</v>
+        <v>12.3499</v>
+      </c>
+      <c r="K244" t="s">
+        <v>857</v>
       </c>
       <c r="L244" s="5" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="245" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
-        <v>45052</v>
+        <v>45051</v>
       </c>
       <c r="B245" s="4">
-        <v>45052</v>
+        <v>45051</v>
       </c>
       <c r="C245" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="D245" t="s">
         <v>13</v>
@@ -12749,34 +12784,34 @@
       <c r="F245" t="s">
         <v>1081</v>
       </c>
-      <c r="G245" s="6" t="s">
-        <v>864</v>
-      </c>
-      <c r="H245" s="6" t="s">
-        <v>864</v>
+      <c r="G245" t="s">
+        <v>860</v>
+      </c>
+      <c r="H245" t="s">
+        <v>860</v>
       </c>
       <c r="I245">
-        <v>37.301099999999998</v>
+        <v>36.721299999999999</v>
       </c>
       <c r="J245">
-        <v>-3.1383999999999999</v>
+        <v>-4.4214000000000002</v>
       </c>
       <c r="K245" s="6" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="L245" s="5" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="246" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
-        <v>45053</v>
+        <v>45052</v>
       </c>
       <c r="B246" s="4">
-        <v>45053</v>
+        <v>45052</v>
       </c>
       <c r="C246" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D246" t="s">
         <v>13</v>
@@ -12788,33 +12823,33 @@
         <v>1081</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="H246" s="6" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="I246">
-        <v>37.615900000000003</v>
+        <v>37.301099999999998</v>
       </c>
       <c r="J246">
-        <v>-0.99160000000000004</v>
+        <v>-3.1383999999999999</v>
       </c>
       <c r="K246" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="L246" s="7" t="s">
-        <v>870</v>
+        <v>865</v>
+      </c>
+      <c r="L246" s="5" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="247" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
-        <v>45054</v>
+        <v>45053</v>
       </c>
       <c r="B247" s="4">
-        <v>45054</v>
+        <v>45053</v>
       </c>
       <c r="C247" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D247" t="s">
         <v>13</v>
@@ -12825,34 +12860,34 @@
       <c r="F247" t="s">
         <v>1081</v>
       </c>
-      <c r="G247" t="s">
-        <v>872</v>
-      </c>
-      <c r="H247" t="s">
-        <v>872</v>
+      <c r="G247" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="H247" s="6" t="s">
+        <v>868</v>
       </c>
       <c r="I247">
-        <v>36.834000000000003</v>
+        <v>37.615900000000003</v>
       </c>
       <c r="J247">
-        <v>-2.4636999999999998</v>
+        <v>-0.99160000000000004</v>
       </c>
       <c r="K247" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="L247" s="5" t="s">
-        <v>874</v>
+        <v>869</v>
+      </c>
+      <c r="L247" s="7" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="248" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
-        <v>45055</v>
+        <v>45054</v>
       </c>
       <c r="B248" s="4">
-        <v>45055</v>
+        <v>45054</v>
       </c>
       <c r="C248" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D248" t="s">
         <v>13</v>
@@ -12876,21 +12911,21 @@
         <v>-2.4636999999999998</v>
       </c>
       <c r="K248" s="6" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="L248" s="5" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="249" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
-        <v>45056</v>
+        <v>45055</v>
       </c>
       <c r="B249" s="4">
-        <v>45056</v>
+        <v>45055</v>
       </c>
       <c r="C249" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D249" t="s">
         <v>13</v>
@@ -12902,33 +12937,33 @@
         <v>1081</v>
       </c>
       <c r="G249" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="H249" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="I249">
-        <v>37.177300000000002</v>
+        <v>36.834000000000003</v>
       </c>
       <c r="J249">
-        <v>-3.5985999999999998</v>
+        <v>-2.4636999999999998</v>
       </c>
       <c r="K249" s="6" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="L249" s="5" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="250" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
-        <v>45057</v>
+        <v>45056</v>
       </c>
       <c r="B250" s="4">
-        <v>45057</v>
-      </c>
-      <c r="C250" s="6" t="s">
-        <v>882</v>
+        <v>45056</v>
+      </c>
+      <c r="C250" t="s">
+        <v>878</v>
       </c>
       <c r="D250" t="s">
         <v>13</v>
@@ -12946,27 +12981,27 @@
         <v>879</v>
       </c>
       <c r="I250">
-        <v>37.177</v>
+        <v>37.177300000000002</v>
       </c>
       <c r="J250">
-        <v>-3.5903999999999998</v>
+        <v>-3.5985999999999998</v>
       </c>
       <c r="K250" s="6" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="L250" s="5" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="251" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
-        <v>45058</v>
+        <v>45057</v>
       </c>
       <c r="B251" s="4">
-        <v>45058</v>
-      </c>
-      <c r="C251" t="s">
-        <v>885</v>
+        <v>45057</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>882</v>
       </c>
       <c r="D251" t="s">
         <v>13</v>
@@ -12978,33 +13013,33 @@
         <v>1081</v>
       </c>
       <c r="G251" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="H251" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="I251">
-        <v>36.878399999999999</v>
+        <v>37.177</v>
       </c>
       <c r="J251">
-        <v>-4.8453999999999997</v>
+        <v>-3.5903999999999998</v>
       </c>
       <c r="K251" s="6" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="L251" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="252" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
-        <v>45059</v>
+        <v>45058</v>
       </c>
       <c r="B252" s="4">
-        <v>45059</v>
+        <v>45058</v>
       </c>
       <c r="C252" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D252" t="s">
         <v>13</v>
@@ -13016,33 +13051,33 @@
         <v>1081</v>
       </c>
       <c r="G252" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="H252" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I252">
-        <v>36.863500000000002</v>
+        <v>36.878399999999999</v>
       </c>
       <c r="J252">
-        <v>-5.181</v>
+        <v>-4.8453999999999997</v>
       </c>
       <c r="K252" s="6" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="L252" s="5" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="253" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
-        <v>45060</v>
+        <v>45059</v>
       </c>
       <c r="B253" s="4">
-        <v>45060</v>
+        <v>45059</v>
       </c>
       <c r="C253" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D253" t="s">
         <v>13</v>
@@ -13054,33 +13089,33 @@
         <v>1081</v>
       </c>
       <c r="G253" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="H253" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I253">
-        <v>36.685000000000002</v>
+        <v>36.863500000000002</v>
       </c>
       <c r="J253">
-        <v>-6.1261000000000001</v>
+        <v>-5.181</v>
       </c>
       <c r="K253" s="6" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="L253" s="5" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="254" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
-        <v>45061</v>
+        <v>45060</v>
       </c>
       <c r="B254" s="4">
-        <v>45061</v>
+        <v>45060</v>
       </c>
       <c r="C254" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="D254" t="s">
         <v>13</v>
@@ -13092,33 +13127,33 @@
         <v>1081</v>
       </c>
       <c r="G254" t="s">
-        <v>39</v>
+        <v>894</v>
       </c>
       <c r="H254" t="s">
-        <v>1082</v>
+        <v>894</v>
       </c>
       <c r="I254">
-        <v>37.389099999999999</v>
+        <v>36.685000000000002</v>
       </c>
       <c r="J254">
-        <v>-5.9844999999999997</v>
+        <v>-6.1261000000000001</v>
       </c>
       <c r="K254" s="6" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="L254" s="5" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
     </row>
     <row r="255" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
-        <v>45062</v>
+        <v>45061</v>
       </c>
       <c r="B255" s="4">
-        <v>45062</v>
+        <v>45061</v>
       </c>
       <c r="C255" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D255" t="s">
         <v>13</v>
@@ -13130,317 +13165,323 @@
         <v>1081</v>
       </c>
       <c r="G255" t="s">
-        <v>901</v>
+        <v>39</v>
       </c>
       <c r="H255" t="s">
-        <v>901</v>
+        <v>1082</v>
       </c>
       <c r="I255">
-        <v>36.192799999999998</v>
+        <v>37.389099999999999</v>
       </c>
       <c r="J255">
-        <v>-5.9227999999999996</v>
+        <v>-5.9844999999999997</v>
       </c>
       <c r="K255" s="6" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="L255" s="5" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="256" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
-        <v>45063</v>
+        <v>45062</v>
       </c>
       <c r="B256" s="4">
-        <v>45063</v>
+        <v>45062</v>
       </c>
       <c r="C256" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="D256" t="s">
         <v>13</v>
       </c>
       <c r="E256" t="s">
-        <v>905</v>
+        <v>38</v>
       </c>
       <c r="F256" t="s">
-        <v>1100</v>
+        <v>1081</v>
       </c>
       <c r="G256" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="H256" t="s">
-        <v>1100</v>
+        <v>901</v>
       </c>
       <c r="I256">
-        <v>36.140799999999999</v>
+        <v>36.192799999999998</v>
       </c>
       <c r="J256">
-        <v>-5.3536000000000001</v>
+        <v>-5.9227999999999996</v>
       </c>
       <c r="K256" s="6" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="L256" s="5" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="257" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
-        <v>45064</v>
+        <v>45063</v>
       </c>
       <c r="B257" s="4">
-        <v>45064</v>
+        <v>45063</v>
       </c>
       <c r="C257" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D257" t="s">
         <v>13</v>
       </c>
       <c r="E257" t="s">
-        <v>38</v>
+        <v>905</v>
       </c>
       <c r="F257" t="s">
-        <v>1081</v>
+        <v>1100</v>
       </c>
       <c r="G257" t="s">
-        <v>860</v>
+        <v>905</v>
       </c>
       <c r="H257" t="s">
-        <v>860</v>
+        <v>1100</v>
       </c>
       <c r="I257">
-        <v>36.721299999999999</v>
+        <v>36.140799999999999</v>
       </c>
       <c r="J257">
-        <v>-4.4214000000000002</v>
+        <v>-5.3536000000000001</v>
       </c>
       <c r="K257" s="6" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="L257" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="258" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
-        <v>45082</v>
+        <v>45064</v>
       </c>
       <c r="B258" s="4">
-        <v>45082</v>
+        <v>45064</v>
       </c>
       <c r="C258" t="s">
-        <v>911</v>
+        <v>908</v>
+      </c>
+      <c r="D258" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258" t="s">
+        <v>38</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G258" t="s">
+        <v>860</v>
+      </c>
+      <c r="H258" t="s">
+        <v>860</v>
+      </c>
+      <c r="I258">
+        <v>36.721299999999999</v>
+      </c>
+      <c r="J258">
+        <v>-4.4214000000000002</v>
+      </c>
+      <c r="K258" s="6" t="s">
+        <v>909</v>
       </c>
       <c r="L258" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="259" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
-        <v>45152</v>
+        <v>45082</v>
       </c>
       <c r="B259" s="4">
-        <v>45155</v>
+        <v>45082</v>
       </c>
       <c r="C259" t="s">
-        <v>913</v>
-      </c>
-      <c r="D259" t="s">
-        <v>13</v>
-      </c>
-      <c r="E259" t="s">
-        <v>14</v>
-      </c>
-      <c r="F259" t="s">
-        <v>1078</v>
-      </c>
-      <c r="K259" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="L259" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="260" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
-        <v>45205</v>
+        <v>45152</v>
       </c>
       <c r="B260" s="4">
-        <v>45257</v>
+        <v>45155</v>
       </c>
       <c r="C260" t="s">
-        <v>916</v>
-      </c>
-      <c r="D260" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="D260" t="s">
         <v>13</v>
       </c>
-      <c r="E260" s="6" t="s">
+      <c r="E260" t="s">
         <v>14</v>
       </c>
-      <c r="F260" s="6" t="s">
+      <c r="F260" t="s">
         <v>1078</v>
       </c>
-      <c r="G260" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H260" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="I260">
-        <v>44.509300000000003</v>
+        <v>46.608800000000002</v>
       </c>
       <c r="J260">
-        <v>11.3589</v>
-      </c>
-      <c r="K260" t="s">
-        <v>917</v>
+        <v>11.766400000000001</v>
+      </c>
+      <c r="K260" s="6" t="s">
+        <v>914</v>
       </c>
       <c r="L260" s="5" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="261" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
-        <v>45222</v>
+        <v>45205</v>
       </c>
       <c r="B261" s="4">
-        <v>45222</v>
+        <v>45257</v>
       </c>
       <c r="C261" t="s">
-        <v>919</v>
+        <v>916</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H261" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I261">
+        <v>44.509300000000003</v>
+      </c>
+      <c r="J261">
+        <v>11.3589</v>
+      </c>
+      <c r="K261" t="s">
+        <v>917</v>
       </c>
       <c r="L261" s="5" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="262" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
-        <v>45246</v>
+        <v>45222</v>
       </c>
       <c r="B262" s="4">
-        <v>45253</v>
+        <v>45222</v>
       </c>
       <c r="C262" t="s">
-        <v>921</v>
-      </c>
-      <c r="D262" t="s">
-        <v>157</v>
-      </c>
-      <c r="E262" t="s">
-        <v>922</v>
-      </c>
-      <c r="F262" t="s">
-        <v>1101</v>
-      </c>
-      <c r="I262">
-        <v>26.820599999999999</v>
-      </c>
-      <c r="J262">
-        <v>30.802499999999998</v>
-      </c>
-      <c r="K262" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="L262" s="5" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="263" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
-        <v>45527</v>
+        <v>45246</v>
       </c>
       <c r="B263" s="4">
-        <v>45532</v>
+        <v>45253</v>
       </c>
       <c r="C263" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D263" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="E263" t="s">
-        <v>14</v>
+        <v>922</v>
       </c>
       <c r="F263" t="s">
-        <v>1078</v>
+        <v>1101</v>
       </c>
       <c r="I263">
-        <v>46.676099999999998</v>
+        <v>26.820599999999999</v>
       </c>
       <c r="J263">
-        <v>11.1609</v>
+        <v>30.802499999999998</v>
       </c>
       <c r="K263" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="L263" s="5" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="264" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
-        <v>45554</v>
+        <v>45527</v>
       </c>
       <c r="B264" s="4">
-        <v>45935</v>
+        <v>45532</v>
       </c>
       <c r="C264" t="s">
-        <v>928</v>
+        <v>925</v>
+      </c>
+      <c r="D264" t="s">
+        <v>13</v>
+      </c>
+      <c r="E264" t="s">
+        <v>14</v>
+      </c>
+      <c r="F264" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I264">
+        <v>46.676099999999998</v>
+      </c>
+      <c r="J264">
+        <v>11.1609</v>
+      </c>
+      <c r="K264" t="s">
+        <v>926</v>
       </c>
       <c r="L264" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="265" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
-        <v>45602</v>
+        <v>45554</v>
       </c>
       <c r="B265" s="4">
-        <v>45603</v>
+        <v>45935</v>
       </c>
       <c r="C265" t="s">
-        <v>930</v>
-      </c>
-      <c r="D265" t="s">
-        <v>164</v>
-      </c>
-      <c r="E265" t="s">
-        <v>931</v>
-      </c>
-      <c r="F265" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G265" t="s">
-        <v>932</v>
-      </c>
-      <c r="H265" t="s">
-        <v>932</v>
-      </c>
-      <c r="I265">
-        <v>36.568399999999997</v>
-      </c>
-      <c r="J265">
-        <v>128.7294</v>
-      </c>
-      <c r="K265" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="L265" s="5" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="266" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
+        <v>45602</v>
+      </c>
+      <c r="B266" s="4">
         <v>45603</v>
       </c>
-      <c r="B266" s="4">
-        <v>45604</v>
-      </c>
       <c r="C266" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="D266" t="s">
         <v>164</v>
@@ -13464,21 +13505,21 @@
         <v>128.7294</v>
       </c>
       <c r="K266" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="L266" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="267" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
-        <v>45605</v>
+        <v>45603</v>
       </c>
       <c r="B267" s="4">
-        <v>45606</v>
+        <v>45604</v>
       </c>
       <c r="C267" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D267" t="s">
         <v>164</v>
@@ -13490,33 +13531,33 @@
         <v>1102</v>
       </c>
       <c r="G267" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="H267" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="I267">
-        <v>35.179600000000001</v>
+        <v>36.568399999999997</v>
       </c>
       <c r="J267">
-        <v>129.07560000000001</v>
+        <v>128.7294</v>
       </c>
       <c r="K267" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="L267" s="5" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="268" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
-        <v>45607</v>
+        <v>45605</v>
       </c>
       <c r="B268" s="4">
-        <v>45607</v>
+        <v>45606</v>
       </c>
       <c r="C268" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D268" t="s">
         <v>164</v>
@@ -13540,21 +13581,21 @@
         <v>129.07560000000001</v>
       </c>
       <c r="K268" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="L268" s="5" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="269" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
-        <v>45608</v>
+        <v>45607</v>
       </c>
       <c r="B269" s="4">
-        <v>45608</v>
+        <v>45607</v>
       </c>
       <c r="C269" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D269" t="s">
         <v>164</v>
@@ -13566,33 +13607,33 @@
         <v>1102</v>
       </c>
       <c r="G269" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="H269" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="I269">
-        <v>35.803600000000003</v>
+        <v>35.179600000000001</v>
       </c>
       <c r="J269">
-        <v>126.88079999999999</v>
+        <v>129.07560000000001</v>
       </c>
       <c r="K269" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="L269" s="5" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="270" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
-        <v>45609</v>
+        <v>45608</v>
       </c>
       <c r="B270" s="4">
-        <v>45609</v>
+        <v>45608</v>
       </c>
       <c r="C270" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="D270" t="s">
         <v>164</v>
@@ -13604,114 +13645,123 @@
         <v>1102</v>
       </c>
       <c r="G270" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H270" t="s">
-        <v>1103</v>
+        <v>946</v>
       </c>
       <c r="I270">
-        <v>37.566499999999998</v>
+        <v>35.803600000000003</v>
       </c>
       <c r="J270">
-        <v>126.97799999999999</v>
+        <v>126.88079999999999</v>
       </c>
       <c r="K270" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="L270" s="5" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="271" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
-        <v>45641</v>
+        <v>45609</v>
       </c>
       <c r="B271" s="4">
-        <v>45641</v>
+        <v>45609</v>
       </c>
       <c r="C271" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="D271" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="E271" t="s">
-        <v>14</v>
+        <v>931</v>
       </c>
       <c r="F271" t="s">
-        <v>1078</v>
+        <v>1102</v>
       </c>
       <c r="G271" t="s">
-        <v>506</v>
+        <v>950</v>
       </c>
       <c r="H271" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="I271">
-        <v>41.902799999999999</v>
+        <v>37.566499999999998</v>
       </c>
       <c r="J271">
-        <v>12.4964</v>
-      </c>
-      <c r="K271" s="6" t="s">
-        <v>954</v>
+        <v>126.97799999999999</v>
+      </c>
+      <c r="K271" t="s">
+        <v>951</v>
       </c>
       <c r="L271" s="5" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="272" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
-        <v>45724</v>
+        <v>45641</v>
       </c>
       <c r="B272" s="4">
-        <v>45724</v>
+        <v>45641</v>
       </c>
       <c r="C272" t="s">
-        <v>956</v>
+        <v>953</v>
+      </c>
+      <c r="D272" t="s">
+        <v>13</v>
+      </c>
+      <c r="E272" t="s">
+        <v>14</v>
+      </c>
+      <c r="F272" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G272" t="s">
+        <v>506</v>
+      </c>
+      <c r="H272" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I272">
+        <v>41.902799999999999</v>
+      </c>
+      <c r="J272">
+        <v>12.4964</v>
+      </c>
+      <c r="K272" s="6" t="s">
+        <v>954</v>
       </c>
       <c r="L272" s="5" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="273" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
-        <v>45745</v>
+        <v>45724</v>
       </c>
       <c r="B273" s="4">
-        <v>45745</v>
+        <v>45724</v>
       </c>
       <c r="C273" t="s">
-        <v>958</v>
-      </c>
-      <c r="D273" t="s">
-        <v>13</v>
-      </c>
-      <c r="E273" t="s">
-        <v>14</v>
-      </c>
-      <c r="F273" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G273" t="s">
-        <v>592</v>
-      </c>
-      <c r="H273" t="s">
-        <v>592</v>
+        <v>956</v>
       </c>
       <c r="L273" s="5" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="274" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
-        <v>45795</v>
+        <v>45745</v>
       </c>
       <c r="B274" s="4">
-        <v>45795</v>
+        <v>45745</v>
       </c>
       <c r="C274" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D274" t="s">
         <v>13</v>
@@ -13723,164 +13773,155 @@
         <v>1078</v>
       </c>
       <c r="G274" t="s">
-        <v>961</v>
+        <v>592</v>
       </c>
       <c r="H274" t="s">
-        <v>961</v>
-      </c>
-      <c r="I274">
-        <v>44.277799999999999</v>
-      </c>
-      <c r="J274">
-        <v>11.001200000000001</v>
-      </c>
-      <c r="K274" t="s">
-        <v>962</v>
+        <v>592</v>
       </c>
       <c r="L274" s="5" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
     </row>
     <row r="275" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
-        <v>45862</v>
+        <v>45795</v>
       </c>
       <c r="B275" s="4">
-        <v>45875</v>
+        <v>45795</v>
       </c>
       <c r="C275" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="D275" t="s">
         <v>13</v>
       </c>
       <c r="E275" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F275" t="s">
-        <v>1079</v>
+        <v>1078</v>
+      </c>
+      <c r="G275" t="s">
+        <v>961</v>
+      </c>
+      <c r="H275" t="s">
+        <v>961</v>
       </c>
       <c r="I275">
-        <v>55.378100000000003</v>
+        <v>44.277799999999999</v>
       </c>
       <c r="J275">
-        <v>-3.4359999999999999</v>
+        <v>11.001200000000001</v>
       </c>
       <c r="K275" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="L275" s="5" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="276" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
-        <v>45935</v>
+        <v>45862</v>
       </c>
       <c r="B276" s="4">
-        <v>45983</v>
+        <v>45875</v>
       </c>
       <c r="C276" t="s">
-        <v>967</v>
+        <v>964</v>
+      </c>
+      <c r="D276" t="s">
+        <v>13</v>
+      </c>
+      <c r="E276" t="s">
+        <v>27</v>
+      </c>
+      <c r="F276" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I276">
+        <v>55.378100000000003</v>
+      </c>
+      <c r="J276">
+        <v>-3.4359999999999999</v>
+      </c>
+      <c r="K276" t="s">
+        <v>965</v>
       </c>
       <c r="L276" s="5" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="277" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
-        <v>46034</v>
+        <v>45935</v>
       </c>
       <c r="B277" s="4">
-        <v>46034</v>
+        <v>45983</v>
       </c>
       <c r="C277" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="L277" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="278" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
-        <v>46103</v>
-      </c>
-      <c r="B278" s="4"/>
+        <v>46034</v>
+      </c>
+      <c r="B278" s="4">
+        <v>46034</v>
+      </c>
       <c r="C278" t="s">
-        <v>971</v>
-      </c>
-      <c r="D278" t="s">
-        <v>13</v>
-      </c>
-      <c r="E278" t="s">
-        <v>14</v>
-      </c>
-      <c r="F278" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G278" t="s">
-        <v>972</v>
-      </c>
-      <c r="H278" t="s">
-        <v>972</v>
-      </c>
-      <c r="I278">
-        <v>46.214399999999998</v>
-      </c>
-      <c r="J278">
-        <v>11.119300000000001</v>
+        <v>969</v>
       </c>
       <c r="L278" s="5" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="279" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
-        <v>46157</v>
-      </c>
-      <c r="B279" s="4">
-        <v>46157</v>
-      </c>
+        <v>46103</v>
+      </c>
+      <c r="B279" s="4"/>
       <c r="C279" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D279" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="E279" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="F279" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
       <c r="G279" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="H279" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="I279">
-        <v>34.6937</v>
+        <v>46.214399999999998</v>
       </c>
       <c r="J279">
-        <v>135.50229999999999</v>
-      </c>
-      <c r="K279" t="s">
-        <v>976</v>
+        <v>11.119300000000001</v>
       </c>
       <c r="L279" s="5" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="280" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="B280" s="4">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="C280" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="D280" t="s">
         <v>164</v>
@@ -13892,33 +13933,33 @@
         <v>1087</v>
       </c>
       <c r="G280" t="s">
-        <v>560</v>
+        <v>975</v>
       </c>
       <c r="H280" t="s">
-        <v>560</v>
+        <v>975</v>
       </c>
       <c r="I280">
-        <v>35.128300000000003</v>
+        <v>34.6937</v>
       </c>
       <c r="J280">
-        <v>136.09809999999999</v>
+        <v>135.50229999999999</v>
       </c>
       <c r="K280" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="L280" s="5" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="281" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="B281" s="4">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="C281" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D281" t="s">
         <v>164</v>
@@ -13930,33 +13971,33 @@
         <v>1087</v>
       </c>
       <c r="G281" t="s">
-        <v>982</v>
+        <v>560</v>
       </c>
       <c r="H281" t="s">
-        <v>982</v>
+        <v>560</v>
       </c>
       <c r="I281">
-        <v>34.459699999999998</v>
+        <v>35.128300000000003</v>
       </c>
       <c r="J281">
-        <v>133.9956</v>
+        <v>136.09809999999999</v>
       </c>
       <c r="K281" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="L281" s="5" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
     </row>
     <row r="282" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="B282" s="4">
-        <v>46160</v>
+        <v>46159</v>
       </c>
       <c r="C282" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="D282" t="s">
         <v>164</v>
@@ -13968,33 +14009,33 @@
         <v>1087</v>
       </c>
       <c r="G282" t="s">
-        <v>333</v>
+        <v>982</v>
       </c>
       <c r="H282" t="s">
-        <v>333</v>
+        <v>982</v>
       </c>
       <c r="I282">
-        <v>34.191000000000003</v>
+        <v>34.459699999999998</v>
       </c>
       <c r="J282">
-        <v>133.82300000000001</v>
+        <v>133.9956</v>
       </c>
       <c r="K282" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="L282" s="5" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="283" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B283" s="4">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="C283" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="D283" t="s">
         <v>164</v>
@@ -14006,33 +14047,33 @@
         <v>1087</v>
       </c>
       <c r="G283" t="s">
-        <v>989</v>
+        <v>333</v>
       </c>
       <c r="H283" t="s">
-        <v>989</v>
+        <v>333</v>
       </c>
       <c r="I283">
-        <v>34.289400000000001</v>
+        <v>34.191000000000003</v>
       </c>
       <c r="J283">
-        <v>133.79769999999999</v>
+        <v>133.82300000000001</v>
       </c>
       <c r="K283" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="L283" s="5" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="284" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B284" s="4">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="C284" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D284" t="s">
         <v>164</v>
@@ -14044,33 +14085,33 @@
         <v>1087</v>
       </c>
       <c r="G284" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="H284" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="I284">
-        <v>33.559699999999999</v>
+        <v>34.289400000000001</v>
       </c>
       <c r="J284">
-        <v>133.53110000000001</v>
+        <v>133.79769999999999</v>
       </c>
       <c r="K284" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="L284" s="5" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
     </row>
     <row r="285" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B285" s="4">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C285" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="D285" t="s">
         <v>164</v>
@@ -14082,33 +14123,33 @@
         <v>1087</v>
       </c>
       <c r="G285" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="H285" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="I285">
-        <v>33.223300000000002</v>
+        <v>33.559699999999999</v>
       </c>
       <c r="J285">
-        <v>132.56059999999999</v>
+        <v>133.53110000000001</v>
       </c>
       <c r="K285" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="L285" s="5" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="286" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B286" s="4">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="C286" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="D286" t="s">
         <v>164</v>
@@ -14120,33 +14161,33 @@
         <v>1087</v>
       </c>
       <c r="G286" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="H286" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="I286">
-        <v>33.839199999999998</v>
+        <v>33.223300000000002</v>
       </c>
       <c r="J286">
-        <v>132.76570000000001</v>
+        <v>132.56059999999999</v>
       </c>
       <c r="K286" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="L286" s="5" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="287" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B287" s="4">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="C287" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D287" t="s">
         <v>164</v>
@@ -14158,33 +14199,33 @@
         <v>1087</v>
       </c>
       <c r="G287" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="H287" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="I287">
-        <v>33.5062</v>
+        <v>33.839199999999998</v>
       </c>
       <c r="J287">
-        <v>132.54470000000001</v>
+        <v>132.76570000000001</v>
       </c>
       <c r="K287" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="L287" s="5" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="288" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B288" s="4">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="C288" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="D288" t="s">
         <v>164</v>
@@ -14196,22 +14237,22 @@
         <v>1087</v>
       </c>
       <c r="G288" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="H288" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="I288">
-        <v>33.839199999999998</v>
+        <v>33.5062</v>
       </c>
       <c r="J288">
-        <v>132.76570000000001</v>
+        <v>132.54470000000001</v>
       </c>
       <c r="K288" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="L288" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="289" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -14222,34 +14263,34 @@
         <v>46166</v>
       </c>
       <c r="C289" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="D289" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="E289" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="F289" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="G289" t="s">
-        <v>51</v>
+        <v>1001</v>
       </c>
       <c r="H289" t="s">
-        <v>51</v>
+        <v>1001</v>
       </c>
       <c r="I289">
-        <v>37.774900000000002</v>
+        <v>33.839199999999998</v>
       </c>
       <c r="J289">
-        <v>-122.4194</v>
-      </c>
-      <c r="K289" s="6" t="s">
-        <v>1012</v>
+        <v>132.76570000000001</v>
+      </c>
+      <c r="K289" t="s">
+        <v>1009</v>
       </c>
       <c r="L289" s="5" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="290" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
